--- a/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-chosen-filters-columns.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-chosen-filters-columns.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\runs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33DC2AA-18B4-467C-9EA6-1A70407EF6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B459D3-FC5A-45E3-8FA3-0955816D1909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,10 +47,741 @@
     <t>Show me the treatment regimen and names of immune checkpoint inhibitors of the class PD1 inhibitors given for non-small cell lung cancer.</t>
   </si>
   <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD1",
-    "Cancer type": "Non-Small Cell Lung Cancer"
+    <t>List the names and clinical setting of all combination ICIs given in melanoma patients.</t>
+  </si>
+  <si>
+    <t>What are the primary endpoints and sample sizes in trials assessing CTLA4 agents in GEJ cancers?</t>
+  </si>
+  <si>
+    <t>Get all phase 3 studies assessing monotherapy for urothelial/bladder cancer and provide follow-up durations for each.</t>
+  </si>
+  <si>
+    <t>Provide treatment and comparator names of trials comparing CTLA4 and PD1 agents in RCC.</t>
+  </si>
+  <si>
+    <t>Provide all information of studies assessing PD-L1 inhibitors.</t>
+  </si>
+  <si>
+    <t>Provide trial names of all the studies where the sample size is equal to or greater than 500.</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Total sample size": "&gt;= 500"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow up",
+    "Column 6": "Study name",
+    "Column 7": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Provide treatment names for all the trials where the primary endpoint is overall survival</t>
+  </si>
+  <si>
+    <t>Provide trial names of all the studies after 2020</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Year": "&gt; 2020"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow up",
+    "Column 6": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which cancers have PD-1 inhibitor monotherapy trials, and what outcomes were measured?	"</t>
+  </si>
+  <si>
+    <t>In which cancers have PD-L1 inhibitors been used in combination therapy?	"</t>
+  </si>
+  <si>
+    <t>Are there trials where a CTLA-4 inhibitor was used alone? Which cancer types?	"</t>
+  </si>
+  <si>
+    <t>Where have CTLA-4 inhibitors been combined with other treatments?	"</t>
+  </si>
+  <si>
+    <t>Which trials in head and neck cancer used PD-1 vs PD-L1 inhibitors?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Class of ICI",
+    "Column 3": "Primary endpoint",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which phase III trials of pembrolizumab in NSCLC are available and what are their NCT numbers?	"</t>
+  </si>
+  <si>
+    <t>List trials of nivolumab in melanoma, noting which are monotherapy vs combination.	"</t>
+  </si>
+  <si>
+    <t>Which trial studied atezolizumab plus chemotherapy in PD-L1 positive triple-negative breast cancer?	"</t>
+  </si>
+  <si>
+    <t>What trials evaluated avelumab in bladder (urothelial) cancer, and what was the clinical setting (e.g., first-line vs maintenance)?	"</t>
+  </si>
+  <si>
+    <t>Has tremelimumab been tested in hepatocellular carcinoma (HCC), for example in combination with other ICIs?	"</t>
+  </si>
+  <si>
+    <t>Was durvalumab studied as maintenance therapy after chemoradiation in Stage III NSCLC (the PACIFIC trial)? Provide details.	"</t>
+  </si>
+  <si>
+    <t>Which Phase 3 trials of PD-1 inhibitors in NSCLC used combination therapy, and what were their sample sizes and primary endpoints?	"</t>
+  </si>
+  <si>
+    <t>Which trials used PD-L1 inhibitors as monotherapy, and in which cancer types?	"</t>
+  </si>
+  <si>
+    <t>Which cancer types have been studied using a dual checkpoint inhibitor combination (PD-1 + CTLA-4)?	"</t>
+  </si>
+  <si>
+    <t>List trials where an ICI was combined with chemotherapy in NSCLC and their primary endpoints.	"</t>
+  </si>
+  <si>
+    <t>In what cancers have ICIs been combined with tyrosine kinase inhibitors (TKIs)?	"</t>
+  </si>
+  <si>
+    <t>Which trials explored combining an ICI with radiotherapy?	"</t>
+  </si>
+  <si>
+    <t>Are there trials combining ICIs with therapeutic cancer vaccines? If so, list them.	"</t>
+  </si>
+  <si>
+    <t>List any trials using the triple combination of an ICI with BRAF and MEK inhibitors in melanoma.	"</t>
+  </si>
+  <si>
+    <t>Which trials combined an ICI with an anti-VEGF therapy (e.g., bevacizumab)?	"</t>
+  </si>
+  <si>
+    <t>Have there been trials using a triplet of ICI + chemotherapy + anti-VEGF? List any and the cancer contexts.	"</t>
+  </si>
+  <si>
+    <t>Which trials employed a regimen of dual ICIs plus chemotherapy?	"</t>
+  </si>
+  <si>
+    <t>Which Phase 3 ICI trials were placebo-controlled?	"</t>
+  </si>
+  <si>
+    <t>Which NSCLC trials had standard chemotherapy as the control arm?	"</t>
+  </si>
+  <si>
+    <t>Which trials in hepatocellular carcinoma used a TKI as the control arm?	"</t>
+  </si>
+  <si>
+    <t>List any trials where the control arm was interferon (e.g., older trials in melanoma or RCC).	"</t>
+  </si>
+  <si>
+    <t>Which trials used best supportive care (BSC) as the control arm?	"</t>
+  </si>
+  <si>
+    <t>Were there any trials comparing ICIs to a combination of chemotherapy plus an EGFR inhibitor (e.g., cetuximab)?	"</t>
+  </si>
+  <si>
+    <t>Identify any trials where the control arm was chemotherapy plus an anti-VEGF agent.	"</t>
+  </si>
+  <si>
+    <t>In any trial was an mTOR inhibitor (e.g., everolimus) used as the control arm (perhaps in RCC)?	"</t>
+  </si>
+  <si>
+    <t>Which trials had a multikinase inhibitor (e.g., sorafenib) as the control treatment?	"</t>
+  </si>
+  <si>
+    <t>Which trials used a therapeutic vaccine as the control arm?	"</t>
+  </si>
+  <si>
+    <t>Was radiotherapy alone ever used as a control arm in these trials?	"</t>
+  </si>
+  <si>
+    <t>Which immunotherapy trials have been conducted in the adjuvant setting for melanoma?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Clinical setting in relation to surgery",
+    "Column 3": "Primary endpoint",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>List any trials using neoadjuvant (pre-surgical) immunotherapy in NSCLC and their primary endpoints.	"</t>
+  </si>
+  <si>
+    <t>Which trials used pathologic complete response (pCR) as a primary endpoint? (Common in neoadjuvant studies.)	"</t>
+  </si>
+  <si>
+    <t>List trials that had objective response rate (ORR) as the primary endpoint.	"</t>
+  </si>
+  <si>
+    <t>Which trials used overall survival (OS) as the primary endpoint?	"</t>
+  </si>
+  <si>
+    <t>Which trials used progression-free survival (PFS) as the primary endpoint?	"</t>
+  </si>
+  <si>
+    <t>In which trials was relapse-free (disease-free) survival (RFS/DFS) the primary endpoint?	"</t>
+  </si>
+  <si>
+    <t>Which trials used event-free survival (EFS) as a primary (or co-primary) endpoint?	"</t>
+  </si>
+  <si>
+    <t>Were there trials primarily focused on safety (with safety as the primary endpoint)?	"</t>
+  </si>
+  <si>
+    <t>Which NSCLC trials required a certain level of PD-L1 expression for enrollment?	"</t>
+  </si>
+  <si>
+    <t>Which immunotherapy trials in colorectal cancer were restricted to MSI-H/dMMR tumors?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Colorectal",
+    "Is any other biomarker used for inclusion": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Is any other biomarker used for inclusion",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Are there immunotherapy trials in pancreatic cancer? If so, did they require a biomarker (e.g., MSI-H) for inclusion?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Pancreatic Cancer",
+    "Is any other biomarker used for inclusion": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Is any other biomarker used for inclusion",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Have immune checkpoint inhibitors been trialed in prostate cancer (perhaps only in biomarker-selected cases)?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Prostate",
+    "Is any other biomarker used for inclusion": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Is any other biomarker used for inclusion",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Are there any trials of ICIs in multiple myeloma? List any and their primary endpoints.	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Multiple Myeloma"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Primary endpoint",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which immunotherapy trials have been conducted in mesothelioma, and what regimens were tested?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Mesothelioma"
+  },
+  "selected_column": {
+    "Column 1": "Treatment regimen",
+    "Column 2": "Trial phase",
+    "Column 3": "Primary endpoint",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which NSCLC trials have follow-up publications with updated results?	"</t>
+  </si>
+  <si>
+    <t>List any follow-up analyses of melanoma immunotherapy trials and their publication details.	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma",
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Year",
+    "Column 3": "Original/Follow Up",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which Phase III trials had co-primary or multiple primary endpoints (e.g., both PFS and OS)?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3, Primary multiple, composite",
+    "or co-primary endpoints?": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "Primary endpoint",
+    "Column 2": "Primary multiple",
+    "Column 3": "composite",
+    "Column 4": "or co-primary endpoints?",
+    "Column 5": "NCT",
+    "Column 6": "PMID",
+    "Column 7": "Authors",
+    "Column 8": "Year",
+    "Column 9": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>For trials where OS was the primary endpoint, what follow-up duration was reported?	"</t>
+  </si>
+  <si>
+    <t>What median follow-up time is reported for trials with PFS as the primary endpoint?	"</t>
+  </si>
+  <si>
+    <t>Identify any immunotherapy trials that had more than two arms (multi-arm trials).	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Number of arms",
+    "Column 3": "Cancer type",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which trials evaluated ICIs as first-line (1L) therapy in advanced NSCLC?	"</t>
+  </si>
+  <si>
+    <t>Which immunotherapy trials studied second-line (post-chemotherapy) treatment in bladder cancer?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Bladder",
+    "Lines of treatment": "2L"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Lines of treatment",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which immunotherapy trials in head and neck cancer were published in the last 2 years, and what were their primary endpoints?	"</t>
+  </si>
+  <si>
+    <t>What is the PubMed ID for the KEYNOTE-024 trial (pembrolizumab vs chemotherapy in NSCLC)?	"</t>
+  </si>
+  <si>
+    <t>Find the NCT identifier for the CheckMate 067 trial (nivolumab + ipilimumab in melanoma).	"</t>
+  </si>
+  <si>
+    <t>Which trials reported quality-of-life outcomes as secondary endpoints?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "Secondary endpoint",
+    "Column 2": "Primary endpoint",
+    "Column 3": "NCT",
+    "Column 4": "PMID",
+    "Column 5": "Authors",
+    "Column 6": "Year",
+    "Column 7": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>What kinds of data are reported in follow-up publications (e.g., updated OS, longer follow-up times)?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of Study": "Follow-up"
+  },
+  "selected_column": {
+    "Column 1": "Type of follow-up given",
+    "Column 2": "NCT",
+    "Column 3": "PMID",
+    "Column 4": "Authors",
+    "Column 5": "Year",
+    "Column 6": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which trials were included in the meta-analysis dataset?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Cancer type",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which trials were excluded from the meta-analysis and did not contribute data?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "No"
+  },
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Cancer type",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>List the original trial publications for immunotherapy in renal cell carcinoma (RCC).	"</t>
+  </si>
+  <si>
+    <t>List all Phase 3 trials in gastric cancer that involved a PD-L1 inhibitor.	"</t>
+  </si>
+  <si>
+    <t>Which trials have investigated PD-1 inhibitors in esophageal or gastroesophageal junction cancers?	"</t>
+  </si>
+  <si>
+    <t>What immunotherapy trials have been conducted in small cell lung cancer (SCLC), and what endpoints did they use?	"</t>
+  </si>
+  <si>
+    <t>Which head and neck cancer trials used overall survival (OS) as a primary endpoint?	"</t>
+  </si>
+  <si>
+    <t>Which immune checkpoint inhibitors have been tested in head and neck cancer trials?	"</t>
+  </si>
+  <si>
+    <t>Which immune checkpoint inhibitors have been evaluated in breast cancer trials?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Class of ICI",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Have ICIs been tested as second-line treatments in gastric cancer? If so, list those trials.	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Gastric/GEJ",
+    "Lines of treatment": "2L"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Lines of treatment",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which immunotherapy trials in hepatocellular carcinoma were first-line versus second-line?	"</t>
+  </si>
+  <si>
+    <t>List immunotherapy trials in RCC, indicating whether they were in the first-line or later-line setting.	"</t>
+  </si>
+  <si>
+    <t>Are there any “perioperative” immunotherapy trials (treatment both before and after surgery)?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Perioperative"
+  },
+  "selected_column": {
+    "Column 1": "Clinical setting in relation to surgery",
+    "Column 2": "Cancer type",
+    "Column 3": "Name of ICI",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which NSCLC trials evaluated an ICI as second-line therapy (after prior treatment failure)?	"</t>
+  </si>
+  <si>
+    <t>Are any trials involving novel checkpoints like LAG-3 or TIGIT inhibitors included in the data?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "No"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Class of ICI",
+    "Column 3": "Cancer type",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Have ICIs been combined with MEK inhibitors in any trials? If so, which ones?	"</t>
+  </si>
+  <si>
+    <t>Which NSCLC trials used PD-1 inhibitors and which used PD-L1 inhibitors (to compare their designs)?	"</t>
+  </si>
+  <si>
+    <t>Which melanoma trials used combination therapy versus monotherapy?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "Name of ICI",
+    "Column 2": "Monotherapy/combination",
+    "Column 3": "Type of combination",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Have combination immunotherapy regimens been studied in head and neck cancer, or are they mostly monotherapy?	"</t>
+  </si>
+  <si>
+    <t>Which NSCLC trials did not require PD-L1 positivity for patient enrollment (all-comer trials)?	"</t>
+  </si>
+  <si>
+    <t>Which cancer types have had Phase III immunotherapy trials conducted?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "Cancer type",
+    "Column 2": "Trial phase",
+    "Column 3": "NCT",
+    "Column 4": "PMID",
+    "Column 5": "Authors",
+    "Column 6": "Year",
+    "Column 7": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which trials combined ICIs with targeted therapies (TKIs or anti-angiogenics) in renal cell carcinoma?	"</t>
+  </si>
+  <si>
+    <t>Have ICIs been combined with chemotherapy in SCLC trials? List any such studies.	"</t>
+  </si>
+  <si>
+    <t>List any NSCLC trials that used a regimen of dual ICIs plus chemotherapy.	"</t>
+  </si>
+  <si>
+    <t>What are the earliest immunotherapy trial publications in this dataset (circa 2010–2012) and which cancers did they involve?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Year": "2010–2012"
+  },
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Year",
+    "Column 3": "Cancer type",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Have dual checkpoint blockade (nivolumab + ipilimumab) trials been done in NSCLC?	"</t>
+  </si>
+  <si>
+    <t>List any trials evaluating ICIs in third-line or later treatment settings (≥3L).	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Lines of treatment": "3L"
+  },
+  "selected_column": {
+    "Column 1": "Cancer type",
+    "Column 2": "Lines of treatment",
+    "Column 3": "Name of ICI",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which trial reported the longest follow-up duration, and what was that duration?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "Study name",
+    "Column 2": "Follow-up duration for primary endpoint(s) in months",
+    "Column 3": "NCT",
+    "Column 4": "PMID",
+    "Column 5": "Authors",
+    "Column 6": "Year",
+    "Column 7": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>What are the publication details (authors, year) for the trial of pembrolizumab in adjuvant melanoma?	"</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -53,12 +797,9 @@
 }</t>
   </si>
   <si>
-    <t>List the names and clinical setting of all combination ICIs given in melanoma patients.</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Monotherapy/combination": "Combination",
+    <t>{
+  "selected_filter": {
+    "Type of Therapy": "Combination Therapy",
     "Cancer Type": "Melanoma"
   },
   "selected_column": {
@@ -75,13 +816,10 @@
 }</t>
   </si>
   <si>
-    <t>What are the primary endpoints and sample sizes in trials assessing CTLA4 agents in GEJ cancers?</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "CTLA4 or any combination of CTLA4",
-    "Cancer type": "GEJ/Esophageal/GEJ"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4 or any combination of CTLA-4",
+    "Cancer Type": "GEJ/Esophageal/GEJ"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -97,14 +835,11 @@
 }</t>
   </si>
   <si>
-    <t>Get all phase 3 studies assessing monotherapy for urothelial/bladder cancer and provide follow-up durations for each.</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3",
-    "Monotherapy/combination": "Monotherapy",
-    "Cancer type": "Urothelial and Bladder"
+    <t>{
+  "selected_filter": {
+    "Trial Phase": "Phase 3",
+    "Type of Therapy": "Monotherapy",
+    "Cancer Type": "Urothelial and Bladder"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -122,8 +857,8 @@
   <si>
     <t>{
   "selected_filter": {
-    "Clinical setting in relation to surgery": "Adjuvant",
-    "Cancer type": "NSCLC"
+    "Clinical Setting": "Adjuvant",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -137,13 +872,10 @@
 }</t>
   </si>
   <si>
-    <t>Provide treatment and comparator names of trials comparing CTLA4 and PD1 agents in RCC.</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD1, CTLA-4 or both",
-    "Cancer type": "Renal cell"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1, CTLA-4 or both",
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -159,12 +891,9 @@
 }</t>
   </si>
   <si>
-    <t>Provide all information of studies assessing PD-L1 inhibitors.</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -177,31 +906,9 @@
 }</t>
   </si>
   <si>
-    <t>Provide trial names of all the studies where the sample size is equal to or greater than 500.</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Total sample size": "&gt;= 500"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Original/Follow up",
-    "Column 6": "Study name",
-    "Column 7": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Provide treatment names for all the trials where the primary endpoint is overall survival</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -215,31 +922,10 @@
 }</t>
   </si>
   <si>
-    <t>Provide trial names of all the studies after 2020</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Year": "&gt; 2020"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Original/Follow up",
-    "Column 6": "Study name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which cancers have PD-1 inhibitor monotherapy trials, and what outcomes were measured?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD1",
-    "Monotherapy/combination": "Monotherapy"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-1",
+    "Type of Therapy": "Monotherapy"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -254,13 +940,10 @@
 }</t>
   </si>
   <si>
-    <t>In which cancers have PD-L1 inhibitors been used in combination therapy?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Combination"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -275,13 +958,10 @@
 }</t>
   </si>
   <si>
-    <t>Are there trials where a CTLA-4 inhibitor was used alone? Which cancer types?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "CTLA4",
-    "Monotherapy/combination": "Monotherapy"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Monotherapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -296,13 +976,10 @@
 }</t>
   </si>
   <si>
-    <t>Where have CTLA-4 inhibitors been combined with other treatments?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "CTLA4",
-    "Monotherapy/combination": "Combination"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "CTLA-4",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -317,32 +994,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials in head and neck cancer used PD-1 vs PD-L1 inhibitors?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck (HNSCC)"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Class of ICI",
-    "Column 3": "Primary endpoint",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which phase III trials of pembrolizumab in NSCLC are available and what are their NCT numbers?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Name of ICI": "Pembrolizumab",
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
     "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Trial Phase": "Phase 3"
   },
@@ -357,12 +1011,9 @@
 }</t>
   </si>
   <si>
-    <t>List trials of nivolumab in melanoma, noting which are monotherapy vs combination.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Name of ICI": "Nivolumab",
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab",
     "Cancer Type": "Melanoma"
   },
   "selected_column": {
@@ -378,14 +1029,11 @@
 }</t>
   </si>
   <si>
-    <t>Which trial studied atezolizumab plus chemotherapy in PD-L1 positive triple-negative breast cancer?	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Cancer Type": "Breast",
-    "Name of ICI": "Atezolizumab",
-    "Type of combination": "ICI + Chemo",
+    "ICI Name": "Atezolizumab",
+    "Type of combination (Treatment Arm)": "ICI + Chemo",
     "Is PD-L1 positivity inclusion criteria": "Yes"
   },
   "selected_column": {
@@ -401,12 +1049,9 @@
 }</t>
   </si>
   <si>
-    <t>What trials evaluated avelumab in bladder (urothelial) cancer, and what was the clinical setting (e.g., first-line vs maintenance)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Name of ICI": "Avelumab",
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
     "Cancer Type": "Bladder"
   },
   "selected_column": {
@@ -422,13 +1067,10 @@
 }</t>
   </si>
   <si>
-    <t>Has tremelimumab been tested in hepatocellular carcinoma (HCC), for example in combination with other ICIs?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Name of ICI": "Tremelimumab",
-    "Cancer Type": "Hepatocellular carcinoma"
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Tremelimumab",
+    "Cancer Type": "Hepatocellular carcinoma (HCC)"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -443,15 +1085,12 @@
 }</t>
   </si>
   <si>
-    <t>Was durvalumab studied as maintenance therapy after chemoradiation in Stage III NSCLC (the PACIFIC trial)? Provide details.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Name of ICI": "Durvalumab",
-    "Cancer Type": "NSCLC",
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Durvalumab",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Clinical Setting": "Maintenance",
-    "Type of control": "Placebo"
+    "Control Arm": "Placebo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -466,15 +1105,12 @@
 }</t>
   </si>
   <si>
-    <t>Which Phase 3 trials of PD-1 inhibitors in NSCLC used combination therapy, and what were their sample sizes and primary endpoints?	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Trial Phase": "Phase 3",
-    "Class of ICI": "PD1",
-    "Cancer Type": "NSCLC",
-    "Monotherapy/combination": "Combination"
+    "ICI Class": "PD-1",
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of Therapy": "Combination Therapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -489,13 +1125,10 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used PD-L1 inhibitors as monotherapy, and in which cancer types?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Monotherapy"
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1",
+    "Type of Therapy": "Monotherapy"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -510,12 +1143,9 @@
 }</t>
   </si>
   <si>
-    <t>Which cancer types have been studied using a dual checkpoint inhibitor combination (PD-1 + CTLA-4)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + ICI"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -530,13 +1160,10 @@
 }</t>
   </si>
   <si>
-    <t>List trials where an ICI was combined with chemotherapy in NSCLC and their primary endpoints.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of combination": "ICI + Chemo"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -551,12 +1178,9 @@
 }</t>
   </si>
   <si>
-    <t>In what cancers have ICIs been combined with tyrosine kinase inhibitors (TKIs)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + TKI"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + TKI"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -571,12 +1195,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials explored combining an ICI with radiotherapy?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Radiation"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Radiation"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -591,12 +1212,9 @@
 }</t>
   </si>
   <si>
-    <t>Are there trials combining ICIs with therapeutic cancer vaccines? If so, list them.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Vaccine"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Vaccine"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -611,12 +1229,9 @@
 }</t>
   </si>
   <si>
-    <t>List any trials using the triple combination of an ICI with BRAF and MEK inhibitors in melanoma.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + BRAFi + MEKi",
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi",
     "Cancer Type": "Melanoma"
   },
   "selected_column": {
@@ -632,12 +1247,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials combined an ICI with an anti-VEGF therapy (e.g., bevacizumab)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Anti-VEGF"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -652,12 +1264,9 @@
 }</t>
   </si>
   <si>
-    <t>Have there been trials using a triplet of ICI + chemotherapy + anti-VEGF? List any and the cancer contexts.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Chemo + Anti-VEGF"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -672,12 +1281,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials employed a regimen of dual ICIs plus chemotherapy?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + ICI + Chemo"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -692,13 +1298,10 @@
 }</t>
   </si>
   <si>
-    <t>Which Phase 3 ICI trials were placebo-controlled?	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Trial Phase": "Phase 3",
-    "Type of control": "Placebo"
+    "Control Arm": "Placebo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -713,13 +1316,10 @@
 }</t>
   </si>
   <si>
-    <t>Which NSCLC trials had standard chemotherapy as the control arm?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of control": "Chemo"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -734,13 +1334,10 @@
 }</t>
   </si>
   <si>
-    <t>Which trials in hepatocellular carcinoma used a TKI as the control arm?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma",
-    "Type of control": "TKI"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Hepatocellular carcinoma (HCC)",
+    "Control Arm": "TKI"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -755,12 +1352,9 @@
 }</t>
   </si>
   <si>
-    <t>List any trials where the control arm was interferon (e.g., older trials in melanoma or RCC).	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Interferon"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Interferon"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -775,12 +1369,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used best supportive care (BSC) as the control arm?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Best Supportive Care"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Best Supportive Care"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -795,12 +1386,9 @@
 }</t>
   </si>
   <si>
-    <t>Were there any trials comparing ICIs to a combination of chemotherapy plus an EGFR inhibitor (e.g., cetuximab)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Chemo / Anti-EGFR"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -815,12 +1403,9 @@
 }</t>
   </si>
   <si>
-    <t>Identify any trials where the control arm was chemotherapy plus an anti-VEGF agent.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Chemo / Anti-VEGF"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-VEGF"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -835,12 +1420,9 @@
 }</t>
   </si>
   <si>
-    <t>In any trial was an mTOR inhibitor (e.g., everolimus) used as the control arm (perhaps in RCC)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "mTOR inhibitor"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "mTOR inhibitor"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -855,12 +1437,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials had a multikinase inhibitor (e.g., sorafenib) as the control treatment?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Multikinase inhibitor"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Multikinase inhibitor"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -875,12 +1454,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used a therapeutic vaccine as the control arm?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Vaccine"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Vaccine"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -895,12 +1471,9 @@
 }</t>
   </si>
   <si>
-    <t>Was radiotherapy alone ever used as a control arm in these trials?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Radiation"
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Radiation"
   },
   "selected_column": {
     "Column 1": "Control regimen",
@@ -915,33 +1488,9 @@
 }</t>
   </si>
   <si>
-    <t>Which immunotherapy trials have been conducted in the adjuvant setting for melanoma?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Clinical Setting": "Adjuvant"
-  },
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Clinical setting in relation to surgery",
-    "Column 3": "Primary endpoint",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>List any trials using neoadjuvant (pre-surgical) immunotherapy in NSCLC and their primary endpoints.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Clinical Setting": "Neoadjuvant"
   },
   "selected_column": {
@@ -957,12 +1506,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used pathologic complete response (pCR) as a primary endpoint? (Common in neoadjuvant studies.)	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "Path CR"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -977,12 +1523,9 @@
 }</t>
   </si>
   <si>
-    <t>List trials that had objective response rate (ORR) as the primary endpoint.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "ORR"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "ORR"
   },
   "selected_column": {
     "Column 1": "Trial phase",
@@ -997,12 +1540,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used overall survival (OS) as the primary endpoint?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "Trial phase",
@@ -1017,12 +1557,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used progression-free survival (PFS) as the primary endpoint?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "PFS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
   },
   "selected_column": {
     "Column 1": "Trial phase",
@@ -1037,12 +1574,9 @@
 }</t>
   </si>
   <si>
-    <t>In which trials was relapse-free (disease-free) survival (RFS/DFS) the primary endpoint?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "RFS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "RFS"
   },
   "selected_column": {
     "Column 1": "Clinical setting in relation to surgery",
@@ -1057,12 +1591,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials used event-free survival (EFS) as a primary (or co-primary) endpoint?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "EFS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "EFS"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -1077,12 +1608,9 @@
 }</t>
   </si>
   <si>
-    <t>Were there trials primarily focused on safety (with safety as the primary endpoint)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "Safety"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1097,12 +1625,9 @@
 }</t>
   </si>
   <si>
-    <t>Which NSCLC trials required a certain level of PD-L1 expression for enrollment?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Is PD-L1 positivity inclusion criteria": "Yes"
   },
   "selected_column": {
@@ -1118,115 +1643,9 @@
 }</t>
   </si>
   <si>
-    <t>Which immunotherapy trials in colorectal cancer were restricted to MSI-H/dMMR tumors?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Colorectal",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Is any other biomarker used for inclusion",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Are there immunotherapy trials in pancreatic cancer? If so, did they require a biomarker (e.g., MSI-H) for inclusion?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Pancreatic Cancer",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Is any other biomarker used for inclusion",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Have immune checkpoint inhibitors been trialed in prostate cancer (perhaps only in biomarker-selected cases)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Prostate",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Is any other biomarker used for inclusion",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Are there any trials of ICIs in multiple myeloma? List any and their primary endpoints.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Multiple Myeloma"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Primary endpoint",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which immunotherapy trials have been conducted in mesothelioma, and what regimens were tested?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Mesothelioma"
-  },
-  "selected_column": {
-    "Column 1": "Treatment regimen",
-    "Column 2": "Trial phase",
-    "Column 3": "Primary endpoint",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which NSCLC trials have follow-up publications with updated results?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Type of Study": "Follow-up"
   },
   "selected_column": {
@@ -1241,54 +1660,9 @@
 }</t>
   </si>
   <si>
-    <t>List any follow-up analyses of melanoma immunotherapy trials and their publication details.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Year",
-    "Column 3": "Original/Follow Up",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which Phase III trials had co-primary or multiple primary endpoints (e.g., both PFS and OS)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3, Primary multiple, composite",
-    "or co-primary endpoints?": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "Primary endpoint",
-    "Column 2": "Primary multiple",
-    "Column 3": "composite",
-    "Column 4": "or co-primary endpoints?",
-    "Column 5": "NCT",
-    "Column 6": "PMID",
-    "Column 7": "Authors",
-    "Column 8": "Year",
-    "Column 9": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>For trials where OS was the primary endpoint, what follow-up duration was reported?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "Follow-up duration for primary endpoint(s) in months",
@@ -1302,12 +1676,9 @@
 }</t>
   </si>
   <si>
-    <t>What median follow-up time is reported for trials with PFS as the primary endpoint?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "PFS"
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
   },
   "selected_column": {
     "Column 1": "Follow-up duration for primary endpoint(s) in months",
@@ -1321,30 +1692,9 @@
 }</t>
   </si>
   <si>
-    <t>Identify any immunotherapy trials that had more than two arms (multi-arm trials).	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Number of arms",
-    "Column 3": "Cancer type",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which trials evaluated ICIs as first-line (1L) therapy in advanced NSCLC?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Lines of treatment": "1L"
   },
   "selected_column": {
@@ -1360,33 +1710,9 @@
 }</t>
   </si>
   <si>
-    <t>Which immunotherapy trials studied second-line (post-chemotherapy) treatment in bladder cancer?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Bladder",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Lines of treatment",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which immunotherapy trials in head and neck cancer were published in the last 2 years, and what were their primary endpoints?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
     "Year": "2023+"
   },
   "selected_column": {
@@ -1401,13 +1727,10 @@
 }</t>
   </si>
   <si>
-    <t>What is the PubMed ID for the KEYNOTE-024 trial (pembrolizumab vs chemotherapy in NSCLC)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Name of ICI": "Pembrolizumab",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "ICI Name": "Pembrolizumab",
     "Is PD-L1 positivity inclusion criteria": "Yes",
     "Trial Phase": "Phase 3"
   },
@@ -1422,13 +1745,10 @@
 }</t>
   </si>
   <si>
-    <t>Find the NCT identifier for the CheckMate 067 trial (nivolumab + ipilimumab in melanoma).	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
-    "Type of combination": "ICI + ICI",
+    "Type of combination (Treatment Arm)": "ICI + ICI",
     "Trial Phase": "Phase 3"
   },
   "selected_column": {
@@ -1442,89 +1762,9 @@
 }</t>
   </si>
   <si>
-    <t>Which trials reported quality-of-life outcomes as secondary endpoints?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "Secondary endpoint",
-    "Column 2": "Primary endpoint",
-    "Column 3": "NCT",
-    "Column 4": "PMID",
-    "Column 5": "Authors",
-    "Column 6": "Year",
-    "Column 7": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>What kinds of data are reported in follow-up publications (e.g., updated OS, longer follow-up times)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "Type of follow-up given",
-    "Column 2": "NCT",
-    "Column 3": "PMID",
-    "Column 4": "Authors",
-    "Column 5": "Year",
-    "Column 6": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which trials were included in the meta-analysis dataset?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Cancer type",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which trials were excluded from the meta-analysis and did not contribute data?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "No"
-  },
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Cancer type",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>List the original trial publications for immunotherapy in renal cell carcinoma (RCC).	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
     "Type of Study": "Original publication"
   },
   "selected_column": {
@@ -1539,14 +1779,11 @@
 }</t>
   </si>
   <si>
-    <t>List all Phase 3 trials in gastric cancer that involved a PD-L1 inhibitor.	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Cancer Type": "Gastric/GEJ",
     "Trial Phase": "Phase 3",
-    "Class of ICI": "PD-L1"
+    "ICI Class": "PD-L1"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1561,13 +1798,10 @@
 }</t>
   </si>
   <si>
-    <t>Which trials have investigated PD-1 inhibitors in esophageal or gastroesophageal junction cancers?	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Cancer Type": "Esophageal/GEJ",
-    "Class of ICI": "PD1"
+    "ICI Class": "PD-1"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1582,12 +1816,9 @@
 }</t>
   </si>
   <si>
-    <t>What immunotherapy trials have been conducted in small cell lung cancer (SCLC), and what endpoints did they use?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -1602,13 +1833,10 @@
 }</t>
   </si>
   <si>
-    <t>Which head and neck cancer trials used overall survival (OS) as a primary endpoint?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck",
-    "Primary endpoint": "OS"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)",
+    "Primary Endpoint": "OS"
   },
   "selected_column": {
     "Column 1": "Study name",
@@ -1623,12 +1851,9 @@
 }</t>
   </si>
   <si>
-    <t>Which immune checkpoint inhibitors have been tested in head and neck cancer trials?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1643,33 +1868,9 @@
 }</t>
   </si>
   <si>
-    <t>Which immune checkpoint inhibitors have been evaluated in breast cancer trials?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Class of ICI",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Have ICIs been tested as second-line treatments in gastric cancer? If so, list those trials.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Gastric/GEJ",
-    "Lines of treatment": "2L"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Hepatocellular carcinoma (HCC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1684,12 +1885,27 @@
 }</t>
   </si>
   <si>
-    <t>Which immunotherapy trials in hepatocellular carcinoma were first-line versus second-line?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Hepatocellular carcinoma"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "Lines of treatment",
+    "Column 2": "Name of ICI",
+    "Column 3": "Trial phase",
+    "Column 4": "NCT",
+    "Column 5": "PMID",
+    "Column 6": "Authors",
+    "Column 7": "Year",
+    "Column 8": "Original/Follow up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Lines of treatment": "2L"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1704,93 +1920,9 @@
 }</t>
   </si>
   <si>
-    <t>List immunotherapy trials in RCC, indicating whether they were in the first-line or later-line setting.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma"
-  },
-  "selected_column": {
-    "Column 1": "Lines of treatment",
-    "Column 2": "Name of ICI",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Are there any “perioperative” immunotherapy trials (treatment both before and after surgery)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical Setting": "Perioperative"
-  },
-  "selected_column": {
-    "Column 1": "Clinical setting in relation to surgery",
-    "Column 2": "Cancer type",
-    "Column 3": "Name of ICI",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which NSCLC trials evaluated an ICI as second-line therapy (after prior treatment failure)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Lines of treatment",
-    "Column 3": "Trial phase",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Are any trials involving novel checkpoints like LAG-3 or TIGIT inhibitors included in the data?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "No"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Class of ICI",
-    "Column 3": "Cancer type",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Have ICIs been combined with MEK inhibitors in any trials? If so, which ones?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + MEKi"
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + MEKi"
   },
   "selected_column": {
     "Column 1": "Cancer type",
@@ -1805,12 +1937,9 @@
 }</t>
   </si>
   <si>
-    <t>Which NSCLC trials used PD-1 inhibitors and which used PD-L1 inhibitors (to compare their designs)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1825,32 +1954,9 @@
 }</t>
   </si>
   <si>
-    <t>Which melanoma trials used combination therapy versus monotherapy?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "Name of ICI",
-    "Column 2": "Monotherapy/combination",
-    "Column 3": "Type of combination",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Have combination immunotherapy regimens been studied in head and neck cancer, or are they mostly monotherapy?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Head and Neck"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Head and Neck (HNSCC)"
   },
   "selected_column": {
     "Column 1": "Name of ICI",
@@ -1865,12 +1971,9 @@
 }</t>
   </si>
   <si>
-    <t>Which NSCLC trials did not require PD-L1 positivity for patient enrollment (all-comer trials)?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
     "Is PD-L1 positivity inclusion criteria": "No"
   },
   "selected_column": {
@@ -1886,32 +1989,10 @@
 }</t>
   </si>
   <si>
-    <t>Which cancer types have had Phase III immunotherapy trials conducted?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial Phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "Cancer type",
-    "Column 2": "Trial phase",
-    "Column 3": "NCT",
-    "Column 4": "PMID",
-    "Column 5": "Authors",
-    "Column 6": "Year",
-    "Column 7": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which trials combined ICIs with targeted therapies (TKIs or anti-angiogenics) in renal cell carcinoma?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Renal Cell Carcinoma",
-    "Type of combination": "ICI + TKI"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1926,13 +2007,10 @@
 }</t>
   </si>
   <si>
-    <t>Have ICIs been combined with chemotherapy in SCLC trials? List any such studies.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "Small Cell Lung Cancer",
-    "Type of combination": "ICI + Chemo"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Small Cell Lung Cancer (SCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1947,13 +2025,10 @@
 }</t>
   </si>
   <si>
-    <t>List any NSCLC trials that used a regimen of dual ICIs plus chemotherapy.	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of combination": "ICI + ICI + Chemo"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -1968,32 +2043,10 @@
 }</t>
   </si>
   <si>
-    <t>What are the earliest immunotherapy trial publications in this dataset (circa 2010–2012) and which cancers did they involve?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Year": "2010–2012"
-  },
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Year",
-    "Column 3": "Cancer type",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Have dual checkpoint blockade (nivolumab + ipilimumab) trials been done in NSCLC?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer Type": "NSCLC",
-    "Type of combination": "ICI + ICI"
+    <t>{
+  "selected_filter": {
+    "Cancer Type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "Treatment regimen",
@@ -2008,50 +2061,10 @@
 }</t>
   </si>
   <si>
-    <t>List any trials evaluating ICIs in third-line or later treatment settings (≥3L).	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Lines of treatment": "3L"
-  },
-  "selected_column": {
-    "Column 1": "Cancer type",
-    "Column 2": "Lines of treatment",
-    "Column 3": "Name of ICI",
-    "Column 4": "NCT",
-    "Column 5": "PMID",
-    "Column 6": "Authors",
-    "Column 7": "Year",
-    "Column 8": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>Which trial reported the longest follow-up duration, and what was that duration?	"</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "Study name",
-    "Column 2": "Follow-up duration for primary endpoint(s) in months",
-    "Column 3": "NCT",
-    "Column 4": "PMID",
-    "Column 5": "Authors",
-    "Column 6": "Year",
-    "Column 7": "Original/Follow up"
-  }
-}</t>
-  </si>
-  <si>
-    <t>What are the publication details (authors, year) for the trial of pembrolizumab in adjuvant melanoma?	"</t>
-  </si>
-  <si>
     <t>{
   "selected_filter": {
     "Cancer Type": "Melanoma",
-    "Name of ICI": "Pembrolizumab",
+    "ICI Name": "Pembrolizumab",
     "Clinical Setting": "Adjuvant"
   },
   "selected_column": {
@@ -2069,11 +2082,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2100,11 +2120,11 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2121,7 +2141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2144,29 +2164,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{67EE0D95-D107-40BC-8452-1F7B4DFA1E1F}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{0FB3FB11-7C5E-4C4D-91D4-7A962640C828}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2386,3498 +2421,3498 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="116.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.5546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="85.5546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="224.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="224.4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="224.4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="237.6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="198" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="224.4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B10" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="171.6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="12" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B12" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="184.8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B13" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B14" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="184.8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B15" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="171.6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B17" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="6" t="s">
+    </row>
+    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="6" t="s">
+    </row>
+    <row r="57" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="6" t="s">
+    </row>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="6" t="s">
+    </row>
+    <row r="59" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="6" t="s">
+    </row>
+    <row r="60" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+    <row r="62" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+    <row r="63" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B63" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+    <row r="66" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="6" t="s">
+    </row>
+    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+    <row r="73" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B73" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B74" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+    <row r="82" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+    <row r="83" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B83" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="B84" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+    <row r="86" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B86" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="B87" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="6" t="s">
+    </row>
+    <row r="88" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="B88" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B89" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="B90" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="6" t="s">
+    </row>
+    <row r="91" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="B91" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B92" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="B93" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="6" t="s">
+    </row>
+    <row r="94" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="B94" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B95" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="B96" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B97" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+    <row r="98" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B98" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="B99" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="6" t="s">
+    </row>
+    <row r="100" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="B100" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="6" t="s">
+    </row>
+    <row r="101" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="5" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="3"/>
+      <c r="B102" s="2"/>
     </row>
     <row r="103" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="3"/>
+      <c r="B103" s="2"/>
     </row>
     <row r="104" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="3"/>
+      <c r="B104" s="2"/>
     </row>
     <row r="105" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="3"/>
+      <c r="B105" s="2"/>
     </row>
     <row r="106" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="3"/>
+      <c r="B106" s="2"/>
     </row>
     <row r="107" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="3"/>
+      <c r="B107" s="2"/>
     </row>
     <row r="108" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="3"/>
+      <c r="B108" s="2"/>
     </row>
     <row r="109" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="3"/>
+      <c r="B109" s="2"/>
     </row>
     <row r="110" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B110" s="3"/>
+      <c r="B110" s="2"/>
     </row>
     <row r="111" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="3"/>
+      <c r="B111" s="2"/>
     </row>
     <row r="112" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="3"/>
+      <c r="B112" s="2"/>
     </row>
     <row r="113" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="3"/>
+      <c r="B113" s="2"/>
     </row>
     <row r="114" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="3"/>
+      <c r="B114" s="2"/>
     </row>
     <row r="115" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="3"/>
+      <c r="B115" s="2"/>
     </row>
     <row r="116" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="3"/>
+      <c r="B116" s="2"/>
     </row>
     <row r="117" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="3"/>
+      <c r="B117" s="2"/>
     </row>
     <row r="118" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="3"/>
+      <c r="B118" s="2"/>
     </row>
     <row r="119" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="3"/>
+      <c r="B119" s="2"/>
     </row>
     <row r="120" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="3"/>
+      <c r="B120" s="2"/>
     </row>
     <row r="121" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="3"/>
+      <c r="B121" s="2"/>
     </row>
     <row r="122" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="3"/>
+      <c r="B122" s="2"/>
     </row>
     <row r="123" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="3"/>
+      <c r="B123" s="2"/>
     </row>
     <row r="124" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="3"/>
+      <c r="B124" s="2"/>
     </row>
     <row r="125" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="3"/>
+      <c r="B125" s="2"/>
     </row>
     <row r="126" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="3"/>
+      <c r="B126" s="2"/>
     </row>
     <row r="127" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="3"/>
+      <c r="B127" s="2"/>
     </row>
     <row r="128" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="3"/>
+      <c r="B128" s="2"/>
     </row>
     <row r="129" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="3"/>
+      <c r="B129" s="2"/>
     </row>
     <row r="130" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="3"/>
+      <c r="B130" s="2"/>
     </row>
     <row r="131" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B131" s="3"/>
+      <c r="B131" s="2"/>
     </row>
     <row r="132" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="3"/>
+      <c r="B132" s="2"/>
     </row>
     <row r="133" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B133" s="3"/>
+      <c r="B133" s="2"/>
     </row>
     <row r="134" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="3"/>
+      <c r="B134" s="2"/>
     </row>
     <row r="135" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B135" s="3"/>
+      <c r="B135" s="2"/>
     </row>
     <row r="136" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B136" s="3"/>
+      <c r="B136" s="2"/>
     </row>
     <row r="137" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B137" s="3"/>
+      <c r="B137" s="2"/>
     </row>
     <row r="138" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B138" s="3"/>
+      <c r="B138" s="2"/>
     </row>
     <row r="139" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B139" s="3"/>
+      <c r="B139" s="2"/>
     </row>
     <row r="140" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B140" s="3"/>
+      <c r="B140" s="2"/>
     </row>
     <row r="141" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B141" s="3"/>
+      <c r="B141" s="2"/>
     </row>
     <row r="142" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B142" s="3"/>
+      <c r="B142" s="2"/>
     </row>
     <row r="143" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B143" s="3"/>
+      <c r="B143" s="2"/>
     </row>
     <row r="144" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B144" s="3"/>
+      <c r="B144" s="2"/>
     </row>
     <row r="145" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B145" s="3"/>
+      <c r="B145" s="2"/>
     </row>
     <row r="146" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B146" s="3"/>
+      <c r="B146" s="2"/>
     </row>
     <row r="147" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B147" s="3"/>
+      <c r="B147" s="2"/>
     </row>
     <row r="148" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B148" s="3"/>
+      <c r="B148" s="2"/>
     </row>
     <row r="149" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B149" s="3"/>
+      <c r="B149" s="2"/>
     </row>
     <row r="150" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B150" s="3"/>
+      <c r="B150" s="2"/>
     </row>
     <row r="151" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B151" s="3"/>
+      <c r="B151" s="2"/>
     </row>
     <row r="152" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B152" s="3"/>
+      <c r="B152" s="2"/>
     </row>
     <row r="153" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B153" s="3"/>
+      <c r="B153" s="2"/>
     </row>
     <row r="154" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B154" s="3"/>
+      <c r="B154" s="2"/>
     </row>
     <row r="155" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B155" s="3"/>
+      <c r="B155" s="2"/>
     </row>
     <row r="156" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B156" s="3"/>
+      <c r="B156" s="2"/>
     </row>
     <row r="157" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B157" s="3"/>
+      <c r="B157" s="2"/>
     </row>
     <row r="158" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B158" s="3"/>
+      <c r="B158" s="2"/>
     </row>
     <row r="159" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B159" s="3"/>
+      <c r="B159" s="2"/>
     </row>
     <row r="160" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B160" s="3"/>
+      <c r="B160" s="2"/>
     </row>
     <row r="161" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B161" s="3"/>
+      <c r="B161" s="2"/>
     </row>
     <row r="162" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="3"/>
+      <c r="B162" s="2"/>
     </row>
     <row r="163" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="3"/>
+      <c r="B163" s="2"/>
     </row>
     <row r="164" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="3"/>
+      <c r="B164" s="2"/>
     </row>
     <row r="165" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="3"/>
+      <c r="B165" s="2"/>
     </row>
     <row r="166" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="3"/>
+      <c r="B166" s="2"/>
     </row>
     <row r="167" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="3"/>
+      <c r="B167" s="2"/>
     </row>
     <row r="168" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B168" s="3"/>
+      <c r="B168" s="2"/>
     </row>
     <row r="169" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B169" s="3"/>
+      <c r="B169" s="2"/>
     </row>
     <row r="170" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B170" s="3"/>
+      <c r="B170" s="2"/>
     </row>
     <row r="171" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B171" s="3"/>
+      <c r="B171" s="2"/>
     </row>
     <row r="172" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B172" s="3"/>
+      <c r="B172" s="2"/>
     </row>
     <row r="173" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B173" s="3"/>
+      <c r="B173" s="2"/>
     </row>
     <row r="174" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B174" s="3"/>
+      <c r="B174" s="2"/>
     </row>
     <row r="175" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B175" s="3"/>
+      <c r="B175" s="2"/>
     </row>
     <row r="176" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B176" s="3"/>
+      <c r="B176" s="2"/>
     </row>
     <row r="177" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B177" s="3"/>
+      <c r="B177" s="2"/>
     </row>
     <row r="178" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B178" s="3"/>
+      <c r="B178" s="2"/>
     </row>
     <row r="179" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B179" s="3"/>
+      <c r="B179" s="2"/>
     </row>
     <row r="180" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B180" s="3"/>
+      <c r="B180" s="2"/>
     </row>
     <row r="181" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B181" s="3"/>
+      <c r="B181" s="2"/>
     </row>
     <row r="182" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B182" s="3"/>
+      <c r="B182" s="2"/>
     </row>
     <row r="183" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B183" s="3"/>
+      <c r="B183" s="2"/>
     </row>
     <row r="184" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B184" s="3"/>
+      <c r="B184" s="2"/>
     </row>
     <row r="185" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B185" s="3"/>
+      <c r="B185" s="2"/>
     </row>
     <row r="186" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B186" s="3"/>
+      <c r="B186" s="2"/>
     </row>
     <row r="187" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B187" s="3"/>
+      <c r="B187" s="2"/>
     </row>
     <row r="188" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B188" s="3"/>
+      <c r="B188" s="2"/>
     </row>
     <row r="189" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B189" s="3"/>
+      <c r="B189" s="2"/>
     </row>
     <row r="190" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B190" s="3"/>
+      <c r="B190" s="2"/>
     </row>
     <row r="191" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B191" s="3"/>
+      <c r="B191" s="2"/>
     </row>
     <row r="192" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B192" s="3"/>
+      <c r="B192" s="2"/>
     </row>
     <row r="193" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B193" s="3"/>
+      <c r="B193" s="2"/>
     </row>
     <row r="194" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B194" s="3"/>
+      <c r="B194" s="2"/>
     </row>
     <row r="195" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B195" s="3"/>
+      <c r="B195" s="2"/>
     </row>
     <row r="196" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B196" s="3"/>
+      <c r="B196" s="2"/>
     </row>
     <row r="197" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B197" s="3"/>
+      <c r="B197" s="2"/>
     </row>
     <row r="198" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B198" s="3"/>
+      <c r="B198" s="2"/>
     </row>
     <row r="199" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B199" s="3"/>
+      <c r="B199" s="2"/>
     </row>
     <row r="200" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B200" s="3"/>
+      <c r="B200" s="2"/>
     </row>
     <row r="201" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B201" s="3"/>
+      <c r="B201" s="2"/>
     </row>
     <row r="202" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B202" s="3"/>
+      <c r="B202" s="2"/>
     </row>
     <row r="203" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B203" s="3"/>
+      <c r="B203" s="2"/>
     </row>
     <row r="204" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B204" s="3"/>
+      <c r="B204" s="2"/>
     </row>
     <row r="205" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B205" s="3"/>
+      <c r="B205" s="2"/>
     </row>
     <row r="206" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B206" s="3"/>
+      <c r="B206" s="2"/>
     </row>
     <row r="207" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B207" s="3"/>
+      <c r="B207" s="2"/>
     </row>
     <row r="208" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B208" s="3"/>
+      <c r="B208" s="2"/>
     </row>
     <row r="209" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B209" s="3"/>
+      <c r="B209" s="2"/>
     </row>
     <row r="210" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B210" s="3"/>
+      <c r="B210" s="2"/>
     </row>
     <row r="211" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B211" s="3"/>
+      <c r="B211" s="2"/>
     </row>
     <row r="212" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B212" s="3"/>
+      <c r="B212" s="2"/>
     </row>
     <row r="213" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B213" s="3"/>
+      <c r="B213" s="2"/>
     </row>
     <row r="214" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B214" s="3"/>
+      <c r="B214" s="2"/>
     </row>
     <row r="215" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B215" s="3"/>
+      <c r="B215" s="2"/>
     </row>
     <row r="216" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B216" s="3"/>
+      <c r="B216" s="2"/>
     </row>
     <row r="217" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B217" s="3"/>
+      <c r="B217" s="2"/>
     </row>
     <row r="218" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B218" s="3"/>
+      <c r="B218" s="2"/>
     </row>
     <row r="219" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B219" s="3"/>
+      <c r="B219" s="2"/>
     </row>
     <row r="220" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B220" s="3"/>
+      <c r="B220" s="2"/>
     </row>
     <row r="221" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B221" s="3"/>
+      <c r="B221" s="2"/>
     </row>
     <row r="222" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B222" s="3"/>
+      <c r="B222" s="2"/>
     </row>
     <row r="223" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B223" s="3"/>
+      <c r="B223" s="2"/>
     </row>
     <row r="224" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B224" s="3"/>
+      <c r="B224" s="2"/>
     </row>
     <row r="225" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B225" s="3"/>
+      <c r="B225" s="2"/>
     </row>
     <row r="226" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B226" s="3"/>
+      <c r="B226" s="2"/>
     </row>
     <row r="227" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B227" s="3"/>
+      <c r="B227" s="2"/>
     </row>
     <row r="228" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B228" s="3"/>
+      <c r="B228" s="2"/>
     </row>
     <row r="229" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B229" s="3"/>
+      <c r="B229" s="2"/>
     </row>
     <row r="230" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B230" s="3"/>
+      <c r="B230" s="2"/>
     </row>
     <row r="231" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B231" s="3"/>
+      <c r="B231" s="2"/>
     </row>
     <row r="232" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B232" s="3"/>
+      <c r="B232" s="2"/>
     </row>
     <row r="233" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B233" s="3"/>
+      <c r="B233" s="2"/>
     </row>
     <row r="234" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B234" s="3"/>
+      <c r="B234" s="2"/>
     </row>
     <row r="235" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B235" s="3"/>
+      <c r="B235" s="2"/>
     </row>
     <row r="236" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B236" s="3"/>
+      <c r="B236" s="2"/>
     </row>
     <row r="237" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B237" s="3"/>
+      <c r="B237" s="2"/>
     </row>
     <row r="238" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B238" s="3"/>
+      <c r="B238" s="2"/>
     </row>
     <row r="239" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B239" s="3"/>
+      <c r="B239" s="2"/>
     </row>
     <row r="240" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B240" s="3"/>
+      <c r="B240" s="2"/>
     </row>
     <row r="241" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B241" s="3"/>
+      <c r="B241" s="2"/>
     </row>
     <row r="242" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B242" s="3"/>
+      <c r="B242" s="2"/>
     </row>
     <row r="243" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B243" s="3"/>
+      <c r="B243" s="2"/>
     </row>
     <row r="244" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B244" s="3"/>
+      <c r="B244" s="2"/>
     </row>
     <row r="245" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B245" s="3"/>
+      <c r="B245" s="2"/>
     </row>
     <row r="246" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B246" s="3"/>
+      <c r="B246" s="2"/>
     </row>
     <row r="247" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B247" s="3"/>
+      <c r="B247" s="2"/>
     </row>
     <row r="248" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B248" s="3"/>
+      <c r="B248" s="2"/>
     </row>
     <row r="249" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B249" s="3"/>
+      <c r="B249" s="2"/>
     </row>
     <row r="250" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B250" s="3"/>
+      <c r="B250" s="2"/>
     </row>
     <row r="251" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B251" s="3"/>
+      <c r="B251" s="2"/>
     </row>
     <row r="252" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B252" s="3"/>
+      <c r="B252" s="2"/>
     </row>
     <row r="253" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B253" s="3"/>
+      <c r="B253" s="2"/>
     </row>
     <row r="254" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B254" s="3"/>
+      <c r="B254" s="2"/>
     </row>
     <row r="255" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B255" s="3"/>
+      <c r="B255" s="2"/>
     </row>
     <row r="256" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B256" s="3"/>
+      <c r="B256" s="2"/>
     </row>
     <row r="257" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B257" s="3"/>
+      <c r="B257" s="2"/>
     </row>
     <row r="258" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B258" s="3"/>
+      <c r="B258" s="2"/>
     </row>
     <row r="259" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B259" s="3"/>
+      <c r="B259" s="2"/>
     </row>
     <row r="260" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B260" s="3"/>
+      <c r="B260" s="2"/>
     </row>
     <row r="261" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B261" s="3"/>
+      <c r="B261" s="2"/>
     </row>
     <row r="262" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B262" s="3"/>
+      <c r="B262" s="2"/>
     </row>
     <row r="263" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B263" s="3"/>
+      <c r="B263" s="2"/>
     </row>
     <row r="264" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B264" s="3"/>
+      <c r="B264" s="2"/>
     </row>
     <row r="265" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B265" s="3"/>
+      <c r="B265" s="2"/>
     </row>
     <row r="266" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B266" s="3"/>
+      <c r="B266" s="2"/>
     </row>
     <row r="267" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B267" s="3"/>
+      <c r="B267" s="2"/>
     </row>
     <row r="268" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B268" s="3"/>
+      <c r="B268" s="2"/>
     </row>
     <row r="269" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B269" s="3"/>
+      <c r="B269" s="2"/>
     </row>
     <row r="270" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B270" s="3"/>
+      <c r="B270" s="2"/>
     </row>
     <row r="271" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B271" s="3"/>
+      <c r="B271" s="2"/>
     </row>
     <row r="272" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B272" s="3"/>
+      <c r="B272" s="2"/>
     </row>
     <row r="273" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B273" s="3"/>
+      <c r="B273" s="2"/>
     </row>
     <row r="274" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B274" s="3"/>
+      <c r="B274" s="2"/>
     </row>
     <row r="275" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B275" s="3"/>
+      <c r="B275" s="2"/>
     </row>
     <row r="276" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B276" s="3"/>
+      <c r="B276" s="2"/>
     </row>
     <row r="277" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B277" s="3"/>
+      <c r="B277" s="2"/>
     </row>
     <row r="278" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B278" s="3"/>
+      <c r="B278" s="2"/>
     </row>
     <row r="279" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B279" s="3"/>
+      <c r="B279" s="2"/>
     </row>
     <row r="280" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B280" s="3"/>
+      <c r="B280" s="2"/>
     </row>
     <row r="281" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B281" s="3"/>
+      <c r="B281" s="2"/>
     </row>
     <row r="282" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B282" s="3"/>
+      <c r="B282" s="2"/>
     </row>
     <row r="283" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B283" s="3"/>
+      <c r="B283" s="2"/>
     </row>
     <row r="284" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B284" s="3"/>
+      <c r="B284" s="2"/>
     </row>
     <row r="285" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B285" s="3"/>
+      <c r="B285" s="2"/>
     </row>
     <row r="286" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B286" s="3"/>
+      <c r="B286" s="2"/>
     </row>
     <row r="287" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B287" s="3"/>
+      <c r="B287" s="2"/>
     </row>
     <row r="288" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B288" s="3"/>
+      <c r="B288" s="2"/>
     </row>
     <row r="289" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B289" s="3"/>
+      <c r="B289" s="2"/>
     </row>
     <row r="290" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B290" s="3"/>
+      <c r="B290" s="2"/>
     </row>
     <row r="291" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B291" s="3"/>
+      <c r="B291" s="2"/>
     </row>
     <row r="292" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B292" s="3"/>
+      <c r="B292" s="2"/>
     </row>
     <row r="293" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B293" s="3"/>
+      <c r="B293" s="2"/>
     </row>
     <row r="294" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B294" s="3"/>
+      <c r="B294" s="2"/>
     </row>
     <row r="295" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B295" s="3"/>
+      <c r="B295" s="2"/>
     </row>
     <row r="296" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B296" s="3"/>
+      <c r="B296" s="2"/>
     </row>
     <row r="297" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B297" s="3"/>
+      <c r="B297" s="2"/>
     </row>
     <row r="298" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B298" s="3"/>
+      <c r="B298" s="2"/>
     </row>
     <row r="299" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B299" s="3"/>
+      <c r="B299" s="2"/>
     </row>
     <row r="300" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B300" s="3"/>
+      <c r="B300" s="2"/>
     </row>
     <row r="301" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B301" s="3"/>
+      <c r="B301" s="2"/>
     </row>
     <row r="302" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B302" s="3"/>
+      <c r="B302" s="2"/>
     </row>
     <row r="303" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B303" s="3"/>
+      <c r="B303" s="2"/>
     </row>
     <row r="304" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B304" s="3"/>
+      <c r="B304" s="2"/>
     </row>
     <row r="305" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B305" s="3"/>
+      <c r="B305" s="2"/>
     </row>
     <row r="306" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B306" s="3"/>
+      <c r="B306" s="2"/>
     </row>
     <row r="307" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B307" s="3"/>
+      <c r="B307" s="2"/>
     </row>
     <row r="308" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B308" s="3"/>
+      <c r="B308" s="2"/>
     </row>
     <row r="309" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B309" s="3"/>
+      <c r="B309" s="2"/>
     </row>
     <row r="310" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B310" s="3"/>
+      <c r="B310" s="2"/>
     </row>
     <row r="311" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B311" s="3"/>
+      <c r="B311" s="2"/>
     </row>
     <row r="312" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B312" s="3"/>
+      <c r="B312" s="2"/>
     </row>
     <row r="313" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B313" s="3"/>
+      <c r="B313" s="2"/>
     </row>
     <row r="314" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B314" s="3"/>
+      <c r="B314" s="2"/>
     </row>
     <row r="315" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B315" s="3"/>
+      <c r="B315" s="2"/>
     </row>
     <row r="316" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B316" s="3"/>
+      <c r="B316" s="2"/>
     </row>
     <row r="317" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B317" s="3"/>
+      <c r="B317" s="2"/>
     </row>
     <row r="318" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B318" s="3"/>
+      <c r="B318" s="2"/>
     </row>
     <row r="319" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B319" s="3"/>
+      <c r="B319" s="2"/>
     </row>
     <row r="320" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B320" s="3"/>
+      <c r="B320" s="2"/>
     </row>
     <row r="321" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B321" s="3"/>
+      <c r="B321" s="2"/>
     </row>
     <row r="322" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B322" s="3"/>
+      <c r="B322" s="2"/>
     </row>
     <row r="323" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B323" s="3"/>
+      <c r="B323" s="2"/>
     </row>
     <row r="324" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B324" s="3"/>
+      <c r="B324" s="2"/>
     </row>
     <row r="325" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B325" s="3"/>
+      <c r="B325" s="2"/>
     </row>
     <row r="326" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B326" s="3"/>
+      <c r="B326" s="2"/>
     </row>
     <row r="327" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B327" s="3"/>
+      <c r="B327" s="2"/>
     </row>
     <row r="328" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B328" s="3"/>
+      <c r="B328" s="2"/>
     </row>
     <row r="329" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B329" s="3"/>
+      <c r="B329" s="2"/>
     </row>
     <row r="330" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B330" s="3"/>
+      <c r="B330" s="2"/>
     </row>
     <row r="331" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B331" s="3"/>
+      <c r="B331" s="2"/>
     </row>
     <row r="332" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B332" s="3"/>
+      <c r="B332" s="2"/>
     </row>
     <row r="333" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B333" s="3"/>
+      <c r="B333" s="2"/>
     </row>
     <row r="334" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B334" s="3"/>
+      <c r="B334" s="2"/>
     </row>
     <row r="335" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B335" s="3"/>
+      <c r="B335" s="2"/>
     </row>
     <row r="336" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B336" s="3"/>
+      <c r="B336" s="2"/>
     </row>
     <row r="337" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B337" s="3"/>
+      <c r="B337" s="2"/>
     </row>
     <row r="338" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B338" s="3"/>
+      <c r="B338" s="2"/>
     </row>
     <row r="339" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B339" s="3"/>
+      <c r="B339" s="2"/>
     </row>
     <row r="340" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B340" s="3"/>
+      <c r="B340" s="2"/>
     </row>
     <row r="341" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B341" s="3"/>
+      <c r="B341" s="2"/>
     </row>
     <row r="342" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B342" s="3"/>
+      <c r="B342" s="2"/>
     </row>
     <row r="343" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B343" s="3"/>
+      <c r="B343" s="2"/>
     </row>
     <row r="344" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B344" s="3"/>
+      <c r="B344" s="2"/>
     </row>
     <row r="345" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B345" s="3"/>
+      <c r="B345" s="2"/>
     </row>
     <row r="346" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B346" s="3"/>
+      <c r="B346" s="2"/>
     </row>
     <row r="347" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B347" s="3"/>
+      <c r="B347" s="2"/>
     </row>
     <row r="348" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B348" s="3"/>
+      <c r="B348" s="2"/>
     </row>
     <row r="349" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B349" s="3"/>
+      <c r="B349" s="2"/>
     </row>
     <row r="350" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B350" s="3"/>
+      <c r="B350" s="2"/>
     </row>
     <row r="351" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B351" s="3"/>
+      <c r="B351" s="2"/>
     </row>
     <row r="352" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B352" s="3"/>
+      <c r="B352" s="2"/>
     </row>
     <row r="353" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B353" s="3"/>
+      <c r="B353" s="2"/>
     </row>
     <row r="354" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B354" s="3"/>
+      <c r="B354" s="2"/>
     </row>
     <row r="355" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B355" s="3"/>
+      <c r="B355" s="2"/>
     </row>
     <row r="356" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B356" s="3"/>
+      <c r="B356" s="2"/>
     </row>
     <row r="357" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B357" s="3"/>
+      <c r="B357" s="2"/>
     </row>
     <row r="358" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B358" s="3"/>
+      <c r="B358" s="2"/>
     </row>
     <row r="359" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B359" s="3"/>
+      <c r="B359" s="2"/>
     </row>
     <row r="360" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B360" s="3"/>
+      <c r="B360" s="2"/>
     </row>
     <row r="361" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B361" s="3"/>
+      <c r="B361" s="2"/>
     </row>
     <row r="362" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B362" s="3"/>
+      <c r="B362" s="2"/>
     </row>
     <row r="363" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B363" s="3"/>
+      <c r="B363" s="2"/>
     </row>
     <row r="364" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B364" s="3"/>
+      <c r="B364" s="2"/>
     </row>
     <row r="365" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B365" s="3"/>
+      <c r="B365" s="2"/>
     </row>
     <row r="366" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B366" s="3"/>
+      <c r="B366" s="2"/>
     </row>
     <row r="367" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B367" s="3"/>
+      <c r="B367" s="2"/>
     </row>
     <row r="368" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B368" s="3"/>
+      <c r="B368" s="2"/>
     </row>
     <row r="369" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B369" s="3"/>
+      <c r="B369" s="2"/>
     </row>
     <row r="370" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B370" s="3"/>
+      <c r="B370" s="2"/>
     </row>
     <row r="371" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B371" s="3"/>
+      <c r="B371" s="2"/>
     </row>
     <row r="372" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B372" s="3"/>
+      <c r="B372" s="2"/>
     </row>
     <row r="373" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B373" s="3"/>
+      <c r="B373" s="2"/>
     </row>
     <row r="374" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B374" s="3"/>
+      <c r="B374" s="2"/>
     </row>
     <row r="375" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B375" s="3"/>
+      <c r="B375" s="2"/>
     </row>
     <row r="376" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B376" s="3"/>
+      <c r="B376" s="2"/>
     </row>
     <row r="377" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B377" s="3"/>
+      <c r="B377" s="2"/>
     </row>
     <row r="378" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B378" s="3"/>
+      <c r="B378" s="2"/>
     </row>
     <row r="379" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B379" s="3"/>
+      <c r="B379" s="2"/>
     </row>
     <row r="380" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B380" s="3"/>
+      <c r="B380" s="2"/>
     </row>
     <row r="381" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B381" s="3"/>
+      <c r="B381" s="2"/>
     </row>
     <row r="382" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B382" s="3"/>
+      <c r="B382" s="2"/>
     </row>
     <row r="383" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B383" s="3"/>
+      <c r="B383" s="2"/>
     </row>
     <row r="384" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B384" s="3"/>
+      <c r="B384" s="2"/>
     </row>
     <row r="385" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B385" s="3"/>
+      <c r="B385" s="2"/>
     </row>
     <row r="386" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B386" s="3"/>
+      <c r="B386" s="2"/>
     </row>
     <row r="387" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B387" s="3"/>
+      <c r="B387" s="2"/>
     </row>
     <row r="388" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B388" s="3"/>
+      <c r="B388" s="2"/>
     </row>
     <row r="389" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B389" s="3"/>
+      <c r="B389" s="2"/>
     </row>
     <row r="390" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B390" s="3"/>
+      <c r="B390" s="2"/>
     </row>
     <row r="391" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B391" s="3"/>
+      <c r="B391" s="2"/>
     </row>
     <row r="392" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B392" s="3"/>
+      <c r="B392" s="2"/>
     </row>
     <row r="393" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B393" s="3"/>
+      <c r="B393" s="2"/>
     </row>
     <row r="394" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B394" s="3"/>
+      <c r="B394" s="2"/>
     </row>
     <row r="395" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B395" s="3"/>
+      <c r="B395" s="2"/>
     </row>
     <row r="396" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B396" s="3"/>
+      <c r="B396" s="2"/>
     </row>
     <row r="397" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B397" s="3"/>
+      <c r="B397" s="2"/>
     </row>
     <row r="398" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B398" s="3"/>
+      <c r="B398" s="2"/>
     </row>
     <row r="399" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B399" s="3"/>
+      <c r="B399" s="2"/>
     </row>
     <row r="400" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B400" s="3"/>
+      <c r="B400" s="2"/>
     </row>
     <row r="401" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B401" s="3"/>
+      <c r="B401" s="2"/>
     </row>
     <row r="402" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B402" s="3"/>
+      <c r="B402" s="2"/>
     </row>
     <row r="403" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B403" s="3"/>
+      <c r="B403" s="2"/>
     </row>
     <row r="404" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B404" s="3"/>
+      <c r="B404" s="2"/>
     </row>
     <row r="405" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B405" s="3"/>
+      <c r="B405" s="2"/>
     </row>
     <row r="406" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B406" s="3"/>
+      <c r="B406" s="2"/>
     </row>
     <row r="407" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B407" s="3"/>
+      <c r="B407" s="2"/>
     </row>
     <row r="408" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B408" s="3"/>
+      <c r="B408" s="2"/>
     </row>
     <row r="409" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B409" s="3"/>
+      <c r="B409" s="2"/>
     </row>
     <row r="410" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B410" s="3"/>
+      <c r="B410" s="2"/>
     </row>
     <row r="411" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B411" s="3"/>
+      <c r="B411" s="2"/>
     </row>
     <row r="412" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B412" s="3"/>
+      <c r="B412" s="2"/>
     </row>
     <row r="413" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B413" s="3"/>
+      <c r="B413" s="2"/>
     </row>
     <row r="414" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B414" s="3"/>
+      <c r="B414" s="2"/>
     </row>
     <row r="415" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B415" s="3"/>
+      <c r="B415" s="2"/>
     </row>
     <row r="416" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B416" s="3"/>
+      <c r="B416" s="2"/>
     </row>
     <row r="417" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B417" s="3"/>
+      <c r="B417" s="2"/>
     </row>
     <row r="418" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B418" s="3"/>
+      <c r="B418" s="2"/>
     </row>
     <row r="419" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B419" s="3"/>
+      <c r="B419" s="2"/>
     </row>
     <row r="420" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B420" s="3"/>
+      <c r="B420" s="2"/>
     </row>
     <row r="421" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B421" s="3"/>
+      <c r="B421" s="2"/>
     </row>
     <row r="422" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B422" s="3"/>
+      <c r="B422" s="2"/>
     </row>
     <row r="423" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B423" s="3"/>
+      <c r="B423" s="2"/>
     </row>
     <row r="424" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B424" s="3"/>
+      <c r="B424" s="2"/>
     </row>
     <row r="425" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B425" s="3"/>
+      <c r="B425" s="2"/>
     </row>
     <row r="426" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B426" s="3"/>
+      <c r="B426" s="2"/>
     </row>
     <row r="427" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B427" s="3"/>
+      <c r="B427" s="2"/>
     </row>
     <row r="428" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B428" s="3"/>
+      <c r="B428" s="2"/>
     </row>
     <row r="429" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B429" s="3"/>
+      <c r="B429" s="2"/>
     </row>
     <row r="430" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B430" s="3"/>
+      <c r="B430" s="2"/>
     </row>
     <row r="431" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B431" s="3"/>
+      <c r="B431" s="2"/>
     </row>
     <row r="432" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B432" s="3"/>
+      <c r="B432" s="2"/>
     </row>
     <row r="433" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B433" s="3"/>
+      <c r="B433" s="2"/>
     </row>
     <row r="434" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B434" s="3"/>
+      <c r="B434" s="2"/>
     </row>
     <row r="435" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B435" s="3"/>
+      <c r="B435" s="2"/>
     </row>
     <row r="436" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B436" s="3"/>
+      <c r="B436" s="2"/>
     </row>
     <row r="437" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B437" s="3"/>
+      <c r="B437" s="2"/>
     </row>
     <row r="438" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B438" s="3"/>
+      <c r="B438" s="2"/>
     </row>
     <row r="439" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B439" s="3"/>
+      <c r="B439" s="2"/>
     </row>
     <row r="440" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B440" s="3"/>
+      <c r="B440" s="2"/>
     </row>
     <row r="441" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B441" s="3"/>
+      <c r="B441" s="2"/>
     </row>
     <row r="442" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B442" s="3"/>
+      <c r="B442" s="2"/>
     </row>
     <row r="443" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B443" s="3"/>
+      <c r="B443" s="2"/>
     </row>
     <row r="444" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B444" s="3"/>
+      <c r="B444" s="2"/>
     </row>
     <row r="445" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B445" s="3"/>
+      <c r="B445" s="2"/>
     </row>
     <row r="446" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B446" s="3"/>
+      <c r="B446" s="2"/>
     </row>
     <row r="447" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B447" s="3"/>
+      <c r="B447" s="2"/>
     </row>
     <row r="448" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B448" s="3"/>
+      <c r="B448" s="2"/>
     </row>
     <row r="449" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B449" s="3"/>
+      <c r="B449" s="2"/>
     </row>
     <row r="450" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B450" s="3"/>
+      <c r="B450" s="2"/>
     </row>
     <row r="451" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B451" s="3"/>
+      <c r="B451" s="2"/>
     </row>
     <row r="452" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B452" s="3"/>
+      <c r="B452" s="2"/>
     </row>
     <row r="453" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B453" s="3"/>
+      <c r="B453" s="2"/>
     </row>
     <row r="454" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B454" s="3"/>
+      <c r="B454" s="2"/>
     </row>
     <row r="455" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B455" s="3"/>
+      <c r="B455" s="2"/>
     </row>
     <row r="456" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B456" s="3"/>
+      <c r="B456" s="2"/>
     </row>
     <row r="457" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B457" s="3"/>
+      <c r="B457" s="2"/>
     </row>
     <row r="458" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B458" s="3"/>
+      <c r="B458" s="2"/>
     </row>
     <row r="459" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B459" s="3"/>
+      <c r="B459" s="2"/>
     </row>
     <row r="460" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B460" s="3"/>
+      <c r="B460" s="2"/>
     </row>
     <row r="461" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B461" s="3"/>
+      <c r="B461" s="2"/>
     </row>
     <row r="462" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B462" s="3"/>
+      <c r="B462" s="2"/>
     </row>
     <row r="463" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B463" s="3"/>
+      <c r="B463" s="2"/>
     </row>
     <row r="464" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B464" s="3"/>
+      <c r="B464" s="2"/>
     </row>
     <row r="465" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B465" s="3"/>
+      <c r="B465" s="2"/>
     </row>
     <row r="466" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B466" s="3"/>
+      <c r="B466" s="2"/>
     </row>
     <row r="467" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B467" s="3"/>
+      <c r="B467" s="2"/>
     </row>
     <row r="468" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B468" s="3"/>
+      <c r="B468" s="2"/>
     </row>
     <row r="469" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B469" s="3"/>
+      <c r="B469" s="2"/>
     </row>
     <row r="470" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B470" s="3"/>
+      <c r="B470" s="2"/>
     </row>
     <row r="471" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B471" s="3"/>
+      <c r="B471" s="2"/>
     </row>
     <row r="472" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B472" s="3"/>
+      <c r="B472" s="2"/>
     </row>
     <row r="473" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B473" s="3"/>
+      <c r="B473" s="2"/>
     </row>
     <row r="474" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B474" s="3"/>
+      <c r="B474" s="2"/>
     </row>
     <row r="475" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B475" s="3"/>
+      <c r="B475" s="2"/>
     </row>
     <row r="476" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B476" s="3"/>
+      <c r="B476" s="2"/>
     </row>
     <row r="477" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B477" s="3"/>
+      <c r="B477" s="2"/>
     </row>
     <row r="478" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B478" s="3"/>
+      <c r="B478" s="2"/>
     </row>
     <row r="479" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B479" s="3"/>
+      <c r="B479" s="2"/>
     </row>
     <row r="480" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B480" s="3"/>
+      <c r="B480" s="2"/>
     </row>
     <row r="481" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B481" s="3"/>
+      <c r="B481" s="2"/>
     </row>
     <row r="482" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B482" s="3"/>
+      <c r="B482" s="2"/>
     </row>
     <row r="483" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B483" s="3"/>
+      <c r="B483" s="2"/>
     </row>
     <row r="484" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B484" s="3"/>
+      <c r="B484" s="2"/>
     </row>
     <row r="485" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B485" s="3"/>
+      <c r="B485" s="2"/>
     </row>
     <row r="486" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B486" s="3"/>
+      <c r="B486" s="2"/>
     </row>
     <row r="487" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B487" s="3"/>
+      <c r="B487" s="2"/>
     </row>
     <row r="488" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B488" s="3"/>
+      <c r="B488" s="2"/>
     </row>
     <row r="489" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B489" s="3"/>
+      <c r="B489" s="2"/>
     </row>
     <row r="490" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B490" s="3"/>
+      <c r="B490" s="2"/>
     </row>
     <row r="491" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B491" s="3"/>
+      <c r="B491" s="2"/>
     </row>
     <row r="492" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B492" s="3"/>
+      <c r="B492" s="2"/>
     </row>
     <row r="493" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B493" s="3"/>
+      <c r="B493" s="2"/>
     </row>
     <row r="494" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B494" s="3"/>
+      <c r="B494" s="2"/>
     </row>
     <row r="495" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B495" s="3"/>
+      <c r="B495" s="2"/>
     </row>
     <row r="496" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B496" s="3"/>
+      <c r="B496" s="2"/>
     </row>
     <row r="497" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B497" s="3"/>
+      <c r="B497" s="2"/>
     </row>
     <row r="498" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B498" s="3"/>
+      <c r="B498" s="2"/>
     </row>
     <row r="499" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B499" s="3"/>
+      <c r="B499" s="2"/>
     </row>
     <row r="500" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B500" s="3"/>
+      <c r="B500" s="2"/>
     </row>
     <row r="501" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B501" s="3"/>
+      <c r="B501" s="2"/>
     </row>
     <row r="502" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B502" s="3"/>
+      <c r="B502" s="2"/>
     </row>
     <row r="503" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B503" s="3"/>
+      <c r="B503" s="2"/>
     </row>
     <row r="504" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B504" s="3"/>
+      <c r="B504" s="2"/>
     </row>
     <row r="505" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B505" s="3"/>
+      <c r="B505" s="2"/>
     </row>
     <row r="506" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B506" s="3"/>
+      <c r="B506" s="2"/>
     </row>
     <row r="507" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B507" s="3"/>
+      <c r="B507" s="2"/>
     </row>
     <row r="508" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B508" s="3"/>
+      <c r="B508" s="2"/>
     </row>
     <row r="509" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B509" s="3"/>
+      <c r="B509" s="2"/>
     </row>
     <row r="510" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B510" s="3"/>
+      <c r="B510" s="2"/>
     </row>
     <row r="511" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B511" s="3"/>
+      <c r="B511" s="2"/>
     </row>
     <row r="512" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B512" s="3"/>
+      <c r="B512" s="2"/>
     </row>
     <row r="513" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B513" s="3"/>
+      <c r="B513" s="2"/>
     </row>
     <row r="514" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B514" s="3"/>
+      <c r="B514" s="2"/>
     </row>
     <row r="515" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B515" s="3"/>
+      <c r="B515" s="2"/>
     </row>
     <row r="516" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B516" s="3"/>
+      <c r="B516" s="2"/>
     </row>
     <row r="517" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B517" s="3"/>
+      <c r="B517" s="2"/>
     </row>
     <row r="518" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B518" s="3"/>
+      <c r="B518" s="2"/>
     </row>
     <row r="519" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B519" s="3"/>
+      <c r="B519" s="2"/>
     </row>
     <row r="520" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B520" s="3"/>
+      <c r="B520" s="2"/>
     </row>
     <row r="521" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B521" s="3"/>
+      <c r="B521" s="2"/>
     </row>
     <row r="522" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B522" s="3"/>
+      <c r="B522" s="2"/>
     </row>
     <row r="523" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B523" s="3"/>
+      <c r="B523" s="2"/>
     </row>
     <row r="524" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B524" s="3"/>
+      <c r="B524" s="2"/>
     </row>
     <row r="525" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B525" s="3"/>
+      <c r="B525" s="2"/>
     </row>
     <row r="526" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B526" s="3"/>
+      <c r="B526" s="2"/>
     </row>
     <row r="527" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B527" s="3"/>
+      <c r="B527" s="2"/>
     </row>
     <row r="528" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B528" s="3"/>
+      <c r="B528" s="2"/>
     </row>
     <row r="529" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B529" s="3"/>
+      <c r="B529" s="2"/>
     </row>
     <row r="530" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B530" s="3"/>
+      <c r="B530" s="2"/>
     </row>
     <row r="531" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B531" s="3"/>
+      <c r="B531" s="2"/>
     </row>
     <row r="532" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B532" s="3"/>
+      <c r="B532" s="2"/>
     </row>
     <row r="533" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B533" s="3"/>
+      <c r="B533" s="2"/>
     </row>
     <row r="534" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B534" s="3"/>
+      <c r="B534" s="2"/>
     </row>
     <row r="535" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B535" s="3"/>
+      <c r="B535" s="2"/>
     </row>
     <row r="536" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B536" s="3"/>
+      <c r="B536" s="2"/>
     </row>
     <row r="537" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B537" s="3"/>
+      <c r="B537" s="2"/>
     </row>
     <row r="538" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B538" s="3"/>
+      <c r="B538" s="2"/>
     </row>
     <row r="539" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B539" s="3"/>
+      <c r="B539" s="2"/>
     </row>
     <row r="540" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B540" s="3"/>
+      <c r="B540" s="2"/>
     </row>
     <row r="541" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B541" s="3"/>
+      <c r="B541" s="2"/>
     </row>
     <row r="542" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B542" s="3"/>
+      <c r="B542" s="2"/>
     </row>
     <row r="543" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B543" s="3"/>
+      <c r="B543" s="2"/>
     </row>
     <row r="544" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B544" s="3"/>
+      <c r="B544" s="2"/>
     </row>
     <row r="545" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B545" s="3"/>
+      <c r="B545" s="2"/>
     </row>
     <row r="546" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B546" s="3"/>
+      <c r="B546" s="2"/>
     </row>
     <row r="547" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B547" s="3"/>
+      <c r="B547" s="2"/>
     </row>
     <row r="548" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B548" s="3"/>
+      <c r="B548" s="2"/>
     </row>
     <row r="549" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B549" s="3"/>
+      <c r="B549" s="2"/>
     </row>
     <row r="550" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B550" s="3"/>
+      <c r="B550" s="2"/>
     </row>
     <row r="551" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B551" s="3"/>
+      <c r="B551" s="2"/>
     </row>
     <row r="552" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B552" s="3"/>
+      <c r="B552" s="2"/>
     </row>
     <row r="553" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B553" s="3"/>
+      <c r="B553" s="2"/>
     </row>
     <row r="554" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B554" s="3"/>
+      <c r="B554" s="2"/>
     </row>
     <row r="555" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B555" s="3"/>
+      <c r="B555" s="2"/>
     </row>
     <row r="556" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B556" s="3"/>
+      <c r="B556" s="2"/>
     </row>
     <row r="557" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B557" s="3"/>
+      <c r="B557" s="2"/>
     </row>
     <row r="558" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B558" s="3"/>
+      <c r="B558" s="2"/>
     </row>
     <row r="559" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B559" s="3"/>
+      <c r="B559" s="2"/>
     </row>
     <row r="560" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B560" s="3"/>
+      <c r="B560" s="2"/>
     </row>
     <row r="561" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B561" s="3"/>
+      <c r="B561" s="2"/>
     </row>
     <row r="562" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B562" s="3"/>
+      <c r="B562" s="2"/>
     </row>
     <row r="563" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B563" s="3"/>
+      <c r="B563" s="2"/>
     </row>
     <row r="564" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B564" s="3"/>
+      <c r="B564" s="2"/>
     </row>
     <row r="565" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B565" s="3"/>
+      <c r="B565" s="2"/>
     </row>
     <row r="566" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B566" s="3"/>
+      <c r="B566" s="2"/>
     </row>
     <row r="567" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B567" s="3"/>
+      <c r="B567" s="2"/>
     </row>
     <row r="568" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B568" s="3"/>
+      <c r="B568" s="2"/>
     </row>
     <row r="569" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B569" s="3"/>
+      <c r="B569" s="2"/>
     </row>
     <row r="570" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B570" s="3"/>
+      <c r="B570" s="2"/>
     </row>
     <row r="571" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B571" s="3"/>
+      <c r="B571" s="2"/>
     </row>
     <row r="572" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B572" s="3"/>
+      <c r="B572" s="2"/>
     </row>
     <row r="573" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B573" s="3"/>
+      <c r="B573" s="2"/>
     </row>
     <row r="574" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B574" s="3"/>
+      <c r="B574" s="2"/>
     </row>
     <row r="575" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B575" s="3"/>
+      <c r="B575" s="2"/>
     </row>
     <row r="576" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B576" s="3"/>
+      <c r="B576" s="2"/>
     </row>
     <row r="577" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B577" s="3"/>
+      <c r="B577" s="2"/>
     </row>
     <row r="578" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B578" s="3"/>
+      <c r="B578" s="2"/>
     </row>
     <row r="579" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B579" s="3"/>
+      <c r="B579" s="2"/>
     </row>
     <row r="580" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B580" s="3"/>
+      <c r="B580" s="2"/>
     </row>
     <row r="581" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B581" s="3"/>
+      <c r="B581" s="2"/>
     </row>
     <row r="582" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B582" s="3"/>
+      <c r="B582" s="2"/>
     </row>
     <row r="583" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B583" s="3"/>
+      <c r="B583" s="2"/>
     </row>
     <row r="584" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B584" s="3"/>
+      <c r="B584" s="2"/>
     </row>
     <row r="585" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B585" s="3"/>
+      <c r="B585" s="2"/>
     </row>
     <row r="586" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B586" s="3"/>
+      <c r="B586" s="2"/>
     </row>
     <row r="587" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B587" s="3"/>
+      <c r="B587" s="2"/>
     </row>
     <row r="588" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B588" s="3"/>
+      <c r="B588" s="2"/>
     </row>
     <row r="589" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B589" s="3"/>
+      <c r="B589" s="2"/>
     </row>
     <row r="590" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B590" s="3"/>
+      <c r="B590" s="2"/>
     </row>
     <row r="591" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B591" s="3"/>
+      <c r="B591" s="2"/>
     </row>
     <row r="592" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B592" s="3"/>
+      <c r="B592" s="2"/>
     </row>
     <row r="593" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B593" s="3"/>
+      <c r="B593" s="2"/>
     </row>
     <row r="594" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B594" s="3"/>
+      <c r="B594" s="2"/>
     </row>
     <row r="595" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B595" s="3"/>
+      <c r="B595" s="2"/>
     </row>
     <row r="596" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B596" s="3"/>
+      <c r="B596" s="2"/>
     </row>
     <row r="597" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B597" s="3"/>
+      <c r="B597" s="2"/>
     </row>
     <row r="598" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B598" s="3"/>
+      <c r="B598" s="2"/>
     </row>
     <row r="599" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B599" s="3"/>
+      <c r="B599" s="2"/>
     </row>
     <row r="600" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B600" s="3"/>
+      <c r="B600" s="2"/>
     </row>
     <row r="601" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B601" s="3"/>
+      <c r="B601" s="2"/>
     </row>
     <row r="602" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B602" s="3"/>
+      <c r="B602" s="2"/>
     </row>
     <row r="603" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B603" s="3"/>
+      <c r="B603" s="2"/>
     </row>
     <row r="604" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B604" s="3"/>
+      <c r="B604" s="2"/>
     </row>
     <row r="605" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B605" s="3"/>
+      <c r="B605" s="2"/>
     </row>
     <row r="606" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B606" s="3"/>
+      <c r="B606" s="2"/>
     </row>
     <row r="607" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B607" s="3"/>
+      <c r="B607" s="2"/>
     </row>
     <row r="608" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B608" s="3"/>
+      <c r="B608" s="2"/>
     </row>
     <row r="609" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B609" s="3"/>
+      <c r="B609" s="2"/>
     </row>
     <row r="610" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B610" s="3"/>
+      <c r="B610" s="2"/>
     </row>
     <row r="611" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B611" s="3"/>
+      <c r="B611" s="2"/>
     </row>
     <row r="612" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B612" s="3"/>
+      <c r="B612" s="2"/>
     </row>
     <row r="613" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B613" s="3"/>
+      <c r="B613" s="2"/>
     </row>
     <row r="614" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B614" s="3"/>
+      <c r="B614" s="2"/>
     </row>
     <row r="615" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B615" s="3"/>
+      <c r="B615" s="2"/>
     </row>
     <row r="616" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B616" s="3"/>
+      <c r="B616" s="2"/>
     </row>
     <row r="617" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B617" s="3"/>
+      <c r="B617" s="2"/>
     </row>
     <row r="618" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B618" s="3"/>
+      <c r="B618" s="2"/>
     </row>
     <row r="619" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B619" s="3"/>
+      <c r="B619" s="2"/>
     </row>
     <row r="620" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B620" s="3"/>
+      <c r="B620" s="2"/>
     </row>
     <row r="621" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B621" s="3"/>
+      <c r="B621" s="2"/>
     </row>
     <row r="622" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B622" s="3"/>
+      <c r="B622" s="2"/>
     </row>
     <row r="623" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B623" s="3"/>
+      <c r="B623" s="2"/>
     </row>
     <row r="624" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B624" s="3"/>
+      <c r="B624" s="2"/>
     </row>
     <row r="625" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B625" s="3"/>
+      <c r="B625" s="2"/>
     </row>
     <row r="626" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B626" s="3"/>
+      <c r="B626" s="2"/>
     </row>
     <row r="627" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B627" s="3"/>
+      <c r="B627" s="2"/>
     </row>
     <row r="628" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B628" s="3"/>
+      <c r="B628" s="2"/>
     </row>
     <row r="629" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B629" s="3"/>
+      <c r="B629" s="2"/>
     </row>
     <row r="630" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B630" s="3"/>
+      <c r="B630" s="2"/>
     </row>
     <row r="631" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B631" s="3"/>
+      <c r="B631" s="2"/>
     </row>
     <row r="632" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B632" s="3"/>
+      <c r="B632" s="2"/>
     </row>
     <row r="633" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B633" s="3"/>
+      <c r="B633" s="2"/>
     </row>
     <row r="634" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B634" s="3"/>
+      <c r="B634" s="2"/>
     </row>
     <row r="635" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B635" s="3"/>
+      <c r="B635" s="2"/>
     </row>
     <row r="636" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B636" s="3"/>
+      <c r="B636" s="2"/>
     </row>
     <row r="637" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B637" s="3"/>
+      <c r="B637" s="2"/>
     </row>
     <row r="638" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B638" s="3"/>
+      <c r="B638" s="2"/>
     </row>
     <row r="639" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B639" s="3"/>
+      <c r="B639" s="2"/>
     </row>
     <row r="640" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B640" s="3"/>
+      <c r="B640" s="2"/>
     </row>
     <row r="641" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B641" s="3"/>
+      <c r="B641" s="2"/>
     </row>
     <row r="642" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B642" s="3"/>
+      <c r="B642" s="2"/>
     </row>
     <row r="643" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B643" s="3"/>
+      <c r="B643" s="2"/>
     </row>
     <row r="644" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B644" s="3"/>
+      <c r="B644" s="2"/>
     </row>
     <row r="645" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B645" s="3"/>
+      <c r="B645" s="2"/>
     </row>
     <row r="646" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B646" s="3"/>
+      <c r="B646" s="2"/>
     </row>
     <row r="647" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B647" s="3"/>
+      <c r="B647" s="2"/>
     </row>
     <row r="648" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B648" s="3"/>
+      <c r="B648" s="2"/>
     </row>
     <row r="649" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B649" s="3"/>
+      <c r="B649" s="2"/>
     </row>
     <row r="650" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B650" s="3"/>
+      <c r="B650" s="2"/>
     </row>
     <row r="651" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B651" s="3"/>
+      <c r="B651" s="2"/>
     </row>
     <row r="652" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B652" s="3"/>
+      <c r="B652" s="2"/>
     </row>
     <row r="653" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B653" s="3"/>
+      <c r="B653" s="2"/>
     </row>
     <row r="654" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B654" s="3"/>
+      <c r="B654" s="2"/>
     </row>
     <row r="655" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B655" s="3"/>
+      <c r="B655" s="2"/>
     </row>
     <row r="656" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B656" s="3"/>
+      <c r="B656" s="2"/>
     </row>
     <row r="657" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B657" s="3"/>
+      <c r="B657" s="2"/>
     </row>
     <row r="658" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B658" s="3"/>
+      <c r="B658" s="2"/>
     </row>
     <row r="659" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B659" s="3"/>
+      <c r="B659" s="2"/>
     </row>
     <row r="660" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B660" s="3"/>
+      <c r="B660" s="2"/>
     </row>
     <row r="661" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B661" s="3"/>
+      <c r="B661" s="2"/>
     </row>
     <row r="662" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B662" s="3"/>
+      <c r="B662" s="2"/>
     </row>
     <row r="663" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B663" s="3"/>
+      <c r="B663" s="2"/>
     </row>
     <row r="664" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B664" s="3"/>
+      <c r="B664" s="2"/>
     </row>
     <row r="665" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B665" s="3"/>
+      <c r="B665" s="2"/>
     </row>
     <row r="666" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B666" s="3"/>
+      <c r="B666" s="2"/>
     </row>
     <row r="667" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B667" s="3"/>
+      <c r="B667" s="2"/>
     </row>
     <row r="668" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B668" s="3"/>
+      <c r="B668" s="2"/>
     </row>
     <row r="669" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B669" s="3"/>
+      <c r="B669" s="2"/>
     </row>
     <row r="670" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B670" s="3"/>
+      <c r="B670" s="2"/>
     </row>
     <row r="671" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B671" s="3"/>
+      <c r="B671" s="2"/>
     </row>
     <row r="672" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B672" s="3"/>
+      <c r="B672" s="2"/>
     </row>
     <row r="673" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B673" s="3"/>
+      <c r="B673" s="2"/>
     </row>
     <row r="674" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B674" s="3"/>
+      <c r="B674" s="2"/>
     </row>
     <row r="675" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B675" s="3"/>
+      <c r="B675" s="2"/>
     </row>
     <row r="676" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B676" s="3"/>
+      <c r="B676" s="2"/>
     </row>
     <row r="677" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B677" s="3"/>
+      <c r="B677" s="2"/>
     </row>
     <row r="678" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B678" s="3"/>
+      <c r="B678" s="2"/>
     </row>
     <row r="679" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B679" s="3"/>
+      <c r="B679" s="2"/>
     </row>
     <row r="680" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B680" s="3"/>
+      <c r="B680" s="2"/>
     </row>
     <row r="681" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B681" s="3"/>
+      <c r="B681" s="2"/>
     </row>
     <row r="682" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B682" s="3"/>
+      <c r="B682" s="2"/>
     </row>
     <row r="683" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B683" s="3"/>
+      <c r="B683" s="2"/>
     </row>
     <row r="684" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B684" s="3"/>
+      <c r="B684" s="2"/>
     </row>
     <row r="685" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B685" s="3"/>
+      <c r="B685" s="2"/>
     </row>
     <row r="686" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B686" s="3"/>
+      <c r="B686" s="2"/>
     </row>
     <row r="687" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B687" s="3"/>
+      <c r="B687" s="2"/>
     </row>
     <row r="688" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B688" s="3"/>
+      <c r="B688" s="2"/>
     </row>
     <row r="689" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B689" s="3"/>
+      <c r="B689" s="2"/>
     </row>
     <row r="690" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B690" s="3"/>
+      <c r="B690" s="2"/>
     </row>
     <row r="691" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B691" s="3"/>
+      <c r="B691" s="2"/>
     </row>
     <row r="692" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B692" s="3"/>
+      <c r="B692" s="2"/>
     </row>
     <row r="693" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B693" s="3"/>
+      <c r="B693" s="2"/>
     </row>
     <row r="694" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B694" s="3"/>
+      <c r="B694" s="2"/>
     </row>
     <row r="695" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B695" s="3"/>
+      <c r="B695" s="2"/>
     </row>
     <row r="696" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B696" s="3"/>
+      <c r="B696" s="2"/>
     </row>
     <row r="697" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B697" s="3"/>
+      <c r="B697" s="2"/>
     </row>
     <row r="698" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B698" s="3"/>
+      <c r="B698" s="2"/>
     </row>
     <row r="699" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B699" s="3"/>
+      <c r="B699" s="2"/>
     </row>
     <row r="700" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B700" s="3"/>
+      <c r="B700" s="2"/>
     </row>
     <row r="701" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B701" s="3"/>
+      <c r="B701" s="2"/>
     </row>
     <row r="702" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B702" s="3"/>
+      <c r="B702" s="2"/>
     </row>
     <row r="703" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B703" s="3"/>
+      <c r="B703" s="2"/>
     </row>
     <row r="704" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B704" s="3"/>
+      <c r="B704" s="2"/>
     </row>
     <row r="705" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B705" s="3"/>
+      <c r="B705" s="2"/>
     </row>
     <row r="706" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B706" s="3"/>
+      <c r="B706" s="2"/>
     </row>
     <row r="707" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B707" s="3"/>
+      <c r="B707" s="2"/>
     </row>
     <row r="708" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B708" s="3"/>
+      <c r="B708" s="2"/>
     </row>
     <row r="709" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B709" s="3"/>
+      <c r="B709" s="2"/>
     </row>
     <row r="710" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B710" s="3"/>
+      <c r="B710" s="2"/>
     </row>
     <row r="711" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B711" s="3"/>
+      <c r="B711" s="2"/>
     </row>
     <row r="712" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B712" s="3"/>
+      <c r="B712" s="2"/>
     </row>
     <row r="713" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B713" s="3"/>
+      <c r="B713" s="2"/>
     </row>
     <row r="714" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B714" s="3"/>
+      <c r="B714" s="2"/>
     </row>
     <row r="715" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B715" s="3"/>
+      <c r="B715" s="2"/>
     </row>
     <row r="716" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B716" s="3"/>
+      <c r="B716" s="2"/>
     </row>
     <row r="717" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B717" s="3"/>
+      <c r="B717" s="2"/>
     </row>
     <row r="718" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B718" s="3"/>
+      <c r="B718" s="2"/>
     </row>
     <row r="719" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B719" s="3"/>
+      <c r="B719" s="2"/>
     </row>
     <row r="720" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B720" s="3"/>
+      <c r="B720" s="2"/>
     </row>
     <row r="721" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B721" s="3"/>
+      <c r="B721" s="2"/>
     </row>
     <row r="722" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B722" s="3"/>
+      <c r="B722" s="2"/>
     </row>
     <row r="723" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B723" s="3"/>
+      <c r="B723" s="2"/>
     </row>
     <row r="724" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B724" s="3"/>
+      <c r="B724" s="2"/>
     </row>
     <row r="725" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B725" s="3"/>
+      <c r="B725" s="2"/>
     </row>
     <row r="726" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B726" s="3"/>
+      <c r="B726" s="2"/>
     </row>
     <row r="727" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B727" s="3"/>
+      <c r="B727" s="2"/>
     </row>
     <row r="728" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B728" s="3"/>
+      <c r="B728" s="2"/>
     </row>
     <row r="729" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B729" s="3"/>
+      <c r="B729" s="2"/>
     </row>
     <row r="730" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B730" s="3"/>
+      <c r="B730" s="2"/>
     </row>
     <row r="731" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B731" s="3"/>
+      <c r="B731" s="2"/>
     </row>
     <row r="732" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B732" s="3"/>
+      <c r="B732" s="2"/>
     </row>
     <row r="733" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B733" s="3"/>
+      <c r="B733" s="2"/>
     </row>
     <row r="734" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B734" s="3"/>
+      <c r="B734" s="2"/>
     </row>
     <row r="735" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B735" s="3"/>
+      <c r="B735" s="2"/>
     </row>
     <row r="736" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B736" s="3"/>
+      <c r="B736" s="2"/>
     </row>
     <row r="737" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B737" s="3"/>
+      <c r="B737" s="2"/>
     </row>
     <row r="738" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B738" s="3"/>
+      <c r="B738" s="2"/>
     </row>
     <row r="739" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B739" s="3"/>
+      <c r="B739" s="2"/>
     </row>
     <row r="740" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B740" s="3"/>
+      <c r="B740" s="2"/>
     </row>
     <row r="741" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B741" s="3"/>
+      <c r="B741" s="2"/>
     </row>
     <row r="742" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B742" s="3"/>
+      <c r="B742" s="2"/>
     </row>
     <row r="743" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B743" s="3"/>
+      <c r="B743" s="2"/>
     </row>
     <row r="744" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B744" s="3"/>
+      <c r="B744" s="2"/>
     </row>
     <row r="745" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B745" s="3"/>
+      <c r="B745" s="2"/>
     </row>
     <row r="746" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B746" s="3"/>
+      <c r="B746" s="2"/>
     </row>
     <row r="747" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B747" s="3"/>
+      <c r="B747" s="2"/>
     </row>
     <row r="748" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B748" s="3"/>
+      <c r="B748" s="2"/>
     </row>
     <row r="749" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B749" s="3"/>
+      <c r="B749" s="2"/>
     </row>
     <row r="750" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B750" s="3"/>
+      <c r="B750" s="2"/>
     </row>
     <row r="751" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B751" s="3"/>
+      <c r="B751" s="2"/>
     </row>
     <row r="752" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B752" s="3"/>
+      <c r="B752" s="2"/>
     </row>
     <row r="753" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B753" s="3"/>
+      <c r="B753" s="2"/>
     </row>
     <row r="754" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B754" s="3"/>
+      <c r="B754" s="2"/>
     </row>
     <row r="755" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B755" s="3"/>
+      <c r="B755" s="2"/>
     </row>
     <row r="756" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B756" s="3"/>
+      <c r="B756" s="2"/>
     </row>
     <row r="757" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B757" s="3"/>
+      <c r="B757" s="2"/>
     </row>
     <row r="758" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B758" s="3"/>
+      <c r="B758" s="2"/>
     </row>
     <row r="759" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B759" s="3"/>
+      <c r="B759" s="2"/>
     </row>
     <row r="760" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B760" s="3"/>
+      <c r="B760" s="2"/>
     </row>
     <row r="761" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B761" s="3"/>
+      <c r="B761" s="2"/>
     </row>
     <row r="762" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B762" s="3"/>
+      <c r="B762" s="2"/>
     </row>
     <row r="763" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B763" s="3"/>
+      <c r="B763" s="2"/>
     </row>
     <row r="764" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B764" s="3"/>
+      <c r="B764" s="2"/>
     </row>
     <row r="765" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B765" s="3"/>
+      <c r="B765" s="2"/>
     </row>
     <row r="766" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B766" s="3"/>
+      <c r="B766" s="2"/>
     </row>
     <row r="767" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B767" s="3"/>
+      <c r="B767" s="2"/>
     </row>
     <row r="768" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B768" s="3"/>
+      <c r="B768" s="2"/>
     </row>
     <row r="769" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B769" s="3"/>
+      <c r="B769" s="2"/>
     </row>
     <row r="770" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B770" s="3"/>
+      <c r="B770" s="2"/>
     </row>
     <row r="771" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B771" s="3"/>
+      <c r="B771" s="2"/>
     </row>
     <row r="772" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B772" s="3"/>
+      <c r="B772" s="2"/>
     </row>
     <row r="773" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B773" s="3"/>
+      <c r="B773" s="2"/>
     </row>
     <row r="774" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B774" s="3"/>
+      <c r="B774" s="2"/>
     </row>
     <row r="775" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B775" s="3"/>
+      <c r="B775" s="2"/>
     </row>
     <row r="776" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B776" s="3"/>
+      <c r="B776" s="2"/>
     </row>
     <row r="777" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B777" s="3"/>
+      <c r="B777" s="2"/>
     </row>
     <row r="778" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B778" s="3"/>
+      <c r="B778" s="2"/>
     </row>
     <row r="779" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B779" s="3"/>
+      <c r="B779" s="2"/>
     </row>
     <row r="780" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B780" s="3"/>
+      <c r="B780" s="2"/>
     </row>
     <row r="781" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B781" s="3"/>
+      <c r="B781" s="2"/>
     </row>
     <row r="782" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B782" s="3"/>
+      <c r="B782" s="2"/>
     </row>
     <row r="783" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B783" s="3"/>
+      <c r="B783" s="2"/>
     </row>
     <row r="784" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B784" s="3"/>
+      <c r="B784" s="2"/>
     </row>
     <row r="785" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B785" s="3"/>
+      <c r="B785" s="2"/>
     </row>
     <row r="786" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B786" s="3"/>
+      <c r="B786" s="2"/>
     </row>
     <row r="787" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B787" s="3"/>
+      <c r="B787" s="2"/>
     </row>
     <row r="788" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B788" s="3"/>
+      <c r="B788" s="2"/>
     </row>
     <row r="789" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B789" s="3"/>
+      <c r="B789" s="2"/>
     </row>
     <row r="790" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B790" s="3"/>
+      <c r="B790" s="2"/>
     </row>
     <row r="791" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B791" s="3"/>
+      <c r="B791" s="2"/>
     </row>
     <row r="792" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B792" s="3"/>
+      <c r="B792" s="2"/>
     </row>
     <row r="793" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B793" s="3"/>
+      <c r="B793" s="2"/>
     </row>
     <row r="794" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B794" s="3"/>
+      <c r="B794" s="2"/>
     </row>
     <row r="795" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B795" s="3"/>
+      <c r="B795" s="2"/>
     </row>
     <row r="796" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B796" s="3"/>
+      <c r="B796" s="2"/>
     </row>
     <row r="797" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B797" s="3"/>
+      <c r="B797" s="2"/>
     </row>
     <row r="798" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B798" s="3"/>
+      <c r="B798" s="2"/>
     </row>
     <row r="799" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B799" s="3"/>
+      <c r="B799" s="2"/>
     </row>
     <row r="800" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B800" s="3"/>
+      <c r="B800" s="2"/>
     </row>
     <row r="801" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B801" s="3"/>
+      <c r="B801" s="2"/>
     </row>
     <row r="802" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B802" s="3"/>
+      <c r="B802" s="2"/>
     </row>
     <row r="803" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B803" s="3"/>
+      <c r="B803" s="2"/>
     </row>
     <row r="804" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B804" s="3"/>
+      <c r="B804" s="2"/>
     </row>
     <row r="805" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B805" s="3"/>
+      <c r="B805" s="2"/>
     </row>
     <row r="806" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B806" s="3"/>
+      <c r="B806" s="2"/>
     </row>
     <row r="807" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B807" s="3"/>
+      <c r="B807" s="2"/>
     </row>
     <row r="808" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B808" s="3"/>
+      <c r="B808" s="2"/>
     </row>
     <row r="809" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B809" s="3"/>
+      <c r="B809" s="2"/>
     </row>
     <row r="810" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B810" s="3"/>
+      <c r="B810" s="2"/>
     </row>
     <row r="811" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B811" s="3"/>
+      <c r="B811" s="2"/>
     </row>
     <row r="812" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B812" s="3"/>
+      <c r="B812" s="2"/>
     </row>
     <row r="813" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B813" s="3"/>
+      <c r="B813" s="2"/>
     </row>
     <row r="814" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B814" s="3"/>
+      <c r="B814" s="2"/>
     </row>
     <row r="815" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B815" s="3"/>
+      <c r="B815" s="2"/>
     </row>
     <row r="816" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B816" s="3"/>
+      <c r="B816" s="2"/>
     </row>
     <row r="817" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B817" s="3"/>
+      <c r="B817" s="2"/>
     </row>
     <row r="818" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B818" s="3"/>
+      <c r="B818" s="2"/>
     </row>
     <row r="819" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B819" s="3"/>
+      <c r="B819" s="2"/>
     </row>
     <row r="820" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B820" s="3"/>
+      <c r="B820" s="2"/>
     </row>
     <row r="821" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B821" s="3"/>
+      <c r="B821" s="2"/>
     </row>
     <row r="822" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B822" s="3"/>
+      <c r="B822" s="2"/>
     </row>
     <row r="823" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B823" s="3"/>
+      <c r="B823" s="2"/>
     </row>
     <row r="824" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B824" s="3"/>
+      <c r="B824" s="2"/>
     </row>
     <row r="825" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B825" s="3"/>
+      <c r="B825" s="2"/>
     </row>
     <row r="826" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B826" s="3"/>
+      <c r="B826" s="2"/>
     </row>
     <row r="827" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B827" s="3"/>
+      <c r="B827" s="2"/>
     </row>
     <row r="828" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B828" s="3"/>
+      <c r="B828" s="2"/>
     </row>
     <row r="829" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B829" s="3"/>
+      <c r="B829" s="2"/>
     </row>
     <row r="830" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B830" s="3"/>
+      <c r="B830" s="2"/>
     </row>
     <row r="831" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B831" s="3"/>
+      <c r="B831" s="2"/>
     </row>
     <row r="832" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B832" s="3"/>
+      <c r="B832" s="2"/>
     </row>
     <row r="833" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B833" s="3"/>
+      <c r="B833" s="2"/>
     </row>
     <row r="834" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B834" s="3"/>
+      <c r="B834" s="2"/>
     </row>
     <row r="835" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B835" s="3"/>
+      <c r="B835" s="2"/>
     </row>
     <row r="836" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B836" s="3"/>
+      <c r="B836" s="2"/>
     </row>
     <row r="837" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B837" s="3"/>
+      <c r="B837" s="2"/>
     </row>
     <row r="838" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B838" s="3"/>
+      <c r="B838" s="2"/>
     </row>
     <row r="839" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B839" s="3"/>
+      <c r="B839" s="2"/>
     </row>
     <row r="840" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B840" s="3"/>
+      <c r="B840" s="2"/>
     </row>
     <row r="841" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B841" s="3"/>
+      <c r="B841" s="2"/>
     </row>
     <row r="842" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B842" s="3"/>
+      <c r="B842" s="2"/>
     </row>
     <row r="843" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B843" s="3"/>
+      <c r="B843" s="2"/>
     </row>
     <row r="844" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B844" s="3"/>
+      <c r="B844" s="2"/>
     </row>
     <row r="845" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B845" s="3"/>
+      <c r="B845" s="2"/>
     </row>
     <row r="846" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B846" s="3"/>
+      <c r="B846" s="2"/>
     </row>
     <row r="847" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B847" s="3"/>
+      <c r="B847" s="2"/>
     </row>
     <row r="848" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B848" s="3"/>
+      <c r="B848" s="2"/>
     </row>
     <row r="849" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B849" s="3"/>
+      <c r="B849" s="2"/>
     </row>
     <row r="850" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B850" s="3"/>
+      <c r="B850" s="2"/>
     </row>
     <row r="851" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B851" s="3"/>
+      <c r="B851" s="2"/>
     </row>
     <row r="852" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B852" s="3"/>
+      <c r="B852" s="2"/>
     </row>
     <row r="853" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B853" s="3"/>
+      <c r="B853" s="2"/>
     </row>
     <row r="854" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B854" s="3"/>
+      <c r="B854" s="2"/>
     </row>
     <row r="855" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B855" s="3"/>
+      <c r="B855" s="2"/>
     </row>
     <row r="856" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B856" s="3"/>
+      <c r="B856" s="2"/>
     </row>
     <row r="857" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B857" s="3"/>
+      <c r="B857" s="2"/>
     </row>
     <row r="858" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B858" s="3"/>
+      <c r="B858" s="2"/>
     </row>
     <row r="859" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B859" s="3"/>
+      <c r="B859" s="2"/>
     </row>
     <row r="860" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B860" s="3"/>
+      <c r="B860" s="2"/>
     </row>
     <row r="861" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B861" s="3"/>
+      <c r="B861" s="2"/>
     </row>
     <row r="862" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B862" s="3"/>
+      <c r="B862" s="2"/>
     </row>
     <row r="863" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B863" s="3"/>
+      <c r="B863" s="2"/>
     </row>
     <row r="864" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B864" s="3"/>
+      <c r="B864" s="2"/>
     </row>
     <row r="865" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B865" s="3"/>
+      <c r="B865" s="2"/>
     </row>
     <row r="866" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B866" s="3"/>
+      <c r="B866" s="2"/>
     </row>
     <row r="867" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B867" s="3"/>
+      <c r="B867" s="2"/>
     </row>
     <row r="868" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B868" s="3"/>
+      <c r="B868" s="2"/>
     </row>
     <row r="869" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B869" s="3"/>
+      <c r="B869" s="2"/>
     </row>
     <row r="870" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B870" s="3"/>
+      <c r="B870" s="2"/>
     </row>
     <row r="871" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B871" s="3"/>
+      <c r="B871" s="2"/>
     </row>
     <row r="872" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B872" s="3"/>
+      <c r="B872" s="2"/>
     </row>
     <row r="873" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B873" s="3"/>
+      <c r="B873" s="2"/>
     </row>
     <row r="874" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B874" s="3"/>
+      <c r="B874" s="2"/>
     </row>
     <row r="875" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B875" s="3"/>
+      <c r="B875" s="2"/>
     </row>
     <row r="876" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B876" s="3"/>
+      <c r="B876" s="2"/>
     </row>
     <row r="877" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B877" s="3"/>
+      <c r="B877" s="2"/>
     </row>
     <row r="878" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B878" s="3"/>
+      <c r="B878" s="2"/>
     </row>
     <row r="879" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B879" s="3"/>
+      <c r="B879" s="2"/>
     </row>
     <row r="880" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B880" s="3"/>
+      <c r="B880" s="2"/>
     </row>
     <row r="881" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B881" s="3"/>
+      <c r="B881" s="2"/>
     </row>
     <row r="882" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B882" s="3"/>
+      <c r="B882" s="2"/>
     </row>
     <row r="883" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B883" s="3"/>
+      <c r="B883" s="2"/>
     </row>
     <row r="884" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B884" s="3"/>
+      <c r="B884" s="2"/>
     </row>
     <row r="885" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B885" s="3"/>
+      <c r="B885" s="2"/>
     </row>
     <row r="886" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B886" s="3"/>
+      <c r="B886" s="2"/>
     </row>
     <row r="887" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B887" s="3"/>
+      <c r="B887" s="2"/>
     </row>
     <row r="888" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B888" s="3"/>
+      <c r="B888" s="2"/>
     </row>
     <row r="889" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B889" s="3"/>
+      <c r="B889" s="2"/>
     </row>
     <row r="890" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B890" s="3"/>
+      <c r="B890" s="2"/>
     </row>
     <row r="891" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B891" s="3"/>
+      <c r="B891" s="2"/>
     </row>
     <row r="892" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B892" s="3"/>
+      <c r="B892" s="2"/>
     </row>
     <row r="893" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B893" s="3"/>
+      <c r="B893" s="2"/>
     </row>
     <row r="894" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B894" s="3"/>
+      <c r="B894" s="2"/>
     </row>
     <row r="895" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B895" s="3"/>
+      <c r="B895" s="2"/>
     </row>
     <row r="896" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B896" s="3"/>
+      <c r="B896" s="2"/>
     </row>
     <row r="897" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B897" s="3"/>
+      <c r="B897" s="2"/>
     </row>
     <row r="898" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B898" s="3"/>
+      <c r="B898" s="2"/>
     </row>
     <row r="899" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B899" s="3"/>
+      <c r="B899" s="2"/>
     </row>
     <row r="900" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B900" s="3"/>
+      <c r="B900" s="2"/>
     </row>
     <row r="901" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B901" s="3"/>
+      <c r="B901" s="2"/>
     </row>
     <row r="902" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B902" s="3"/>
+      <c r="B902" s="2"/>
     </row>
     <row r="903" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B903" s="3"/>
+      <c r="B903" s="2"/>
     </row>
     <row r="904" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B904" s="3"/>
+      <c r="B904" s="2"/>
     </row>
     <row r="905" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B905" s="3"/>
+      <c r="B905" s="2"/>
     </row>
     <row r="906" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B906" s="3"/>
+      <c r="B906" s="2"/>
     </row>
     <row r="907" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B907" s="3"/>
+      <c r="B907" s="2"/>
     </row>
     <row r="908" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B908" s="3"/>
+      <c r="B908" s="2"/>
     </row>
     <row r="909" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B909" s="3"/>
+      <c r="B909" s="2"/>
     </row>
     <row r="910" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B910" s="3"/>
+      <c r="B910" s="2"/>
     </row>
     <row r="911" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B911" s="3"/>
+      <c r="B911" s="2"/>
     </row>
     <row r="912" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B912" s="3"/>
+      <c r="B912" s="2"/>
     </row>
     <row r="913" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B913" s="3"/>
+      <c r="B913" s="2"/>
     </row>
     <row r="914" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B914" s="3"/>
+      <c r="B914" s="2"/>
     </row>
     <row r="915" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B915" s="3"/>
+      <c r="B915" s="2"/>
     </row>
     <row r="916" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B916" s="3"/>
+      <c r="B916" s="2"/>
     </row>
     <row r="917" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B917" s="3"/>
+      <c r="B917" s="2"/>
     </row>
     <row r="918" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B918" s="3"/>
+      <c r="B918" s="2"/>
     </row>
     <row r="919" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B919" s="3"/>
+      <c r="B919" s="2"/>
     </row>
     <row r="920" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B920" s="3"/>
+      <c r="B920" s="2"/>
     </row>
     <row r="921" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B921" s="3"/>
+      <c r="B921" s="2"/>
     </row>
     <row r="922" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B922" s="3"/>
+      <c r="B922" s="2"/>
     </row>
     <row r="923" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B923" s="3"/>
+      <c r="B923" s="2"/>
     </row>
     <row r="924" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B924" s="3"/>
+      <c r="B924" s="2"/>
     </row>
     <row r="925" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B925" s="3"/>
+      <c r="B925" s="2"/>
     </row>
     <row r="926" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B926" s="3"/>
+      <c r="B926" s="2"/>
     </row>
     <row r="927" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B927" s="3"/>
+      <c r="B927" s="2"/>
     </row>
     <row r="928" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B928" s="3"/>
+      <c r="B928" s="2"/>
     </row>
     <row r="929" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B929" s="3"/>
+      <c r="B929" s="2"/>
     </row>
     <row r="930" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B930" s="3"/>
+      <c r="B930" s="2"/>
     </row>
     <row r="931" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B931" s="3"/>
+      <c r="B931" s="2"/>
     </row>
     <row r="932" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B932" s="3"/>
+      <c r="B932" s="2"/>
     </row>
     <row r="933" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B933" s="3"/>
+      <c r="B933" s="2"/>
     </row>
     <row r="934" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B934" s="3"/>
+      <c r="B934" s="2"/>
     </row>
     <row r="935" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B935" s="3"/>
+      <c r="B935" s="2"/>
     </row>
     <row r="936" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B936" s="3"/>
+      <c r="B936" s="2"/>
     </row>
     <row r="937" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B937" s="3"/>
+      <c r="B937" s="2"/>
     </row>
     <row r="938" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B938" s="3"/>
+      <c r="B938" s="2"/>
     </row>
     <row r="939" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B939" s="3"/>
+      <c r="B939" s="2"/>
     </row>
     <row r="940" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B940" s="3"/>
+      <c r="B940" s="2"/>
     </row>
     <row r="941" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B941" s="3"/>
+      <c r="B941" s="2"/>
     </row>
     <row r="942" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B942" s="3"/>
+      <c r="B942" s="2"/>
     </row>
     <row r="943" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B943" s="3"/>
+      <c r="B943" s="2"/>
     </row>
     <row r="944" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B944" s="3"/>
+      <c r="B944" s="2"/>
     </row>
     <row r="945" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B945" s="3"/>
+      <c r="B945" s="2"/>
     </row>
     <row r="946" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B946" s="3"/>
+      <c r="B946" s="2"/>
     </row>
     <row r="947" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B947" s="3"/>
+      <c r="B947" s="2"/>
     </row>
     <row r="948" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B948" s="3"/>
+      <c r="B948" s="2"/>
     </row>
     <row r="949" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B949" s="3"/>
+      <c r="B949" s="2"/>
     </row>
     <row r="950" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B950" s="3"/>
+      <c r="B950" s="2"/>
     </row>
     <row r="951" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B951" s="3"/>
+      <c r="B951" s="2"/>
     </row>
     <row r="952" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B952" s="3"/>
+      <c r="B952" s="2"/>
     </row>
     <row r="953" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B953" s="3"/>
+      <c r="B953" s="2"/>
     </row>
     <row r="954" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B954" s="3"/>
+      <c r="B954" s="2"/>
     </row>
     <row r="955" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B955" s="3"/>
+      <c r="B955" s="2"/>
     </row>
     <row r="956" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B956" s="3"/>
+      <c r="B956" s="2"/>
     </row>
     <row r="957" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B957" s="3"/>
+      <c r="B957" s="2"/>
     </row>
     <row r="958" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B958" s="3"/>
+      <c r="B958" s="2"/>
     </row>
     <row r="959" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B959" s="3"/>
+      <c r="B959" s="2"/>
     </row>
     <row r="960" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B960" s="3"/>
+      <c r="B960" s="2"/>
     </row>
     <row r="961" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B961" s="3"/>
+      <c r="B961" s="2"/>
     </row>
     <row r="962" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B962" s="3"/>
+      <c r="B962" s="2"/>
     </row>
     <row r="963" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B963" s="3"/>
+      <c r="B963" s="2"/>
     </row>
     <row r="964" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B964" s="3"/>
+      <c r="B964" s="2"/>
     </row>
     <row r="965" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B965" s="3"/>
+      <c r="B965" s="2"/>
     </row>
     <row r="966" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B966" s="3"/>
+      <c r="B966" s="2"/>
     </row>
     <row r="967" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B967" s="3"/>
+      <c r="B967" s="2"/>
     </row>
     <row r="968" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B968" s="3"/>
+      <c r="B968" s="2"/>
     </row>
     <row r="969" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B969" s="3"/>
+      <c r="B969" s="2"/>
     </row>
     <row r="970" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B970" s="3"/>
+      <c r="B970" s="2"/>
     </row>
     <row r="971" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B971" s="3"/>
+      <c r="B971" s="2"/>
     </row>
     <row r="972" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B972" s="3"/>
+      <c r="B972" s="2"/>
     </row>
     <row r="973" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B973" s="3"/>
+      <c r="B973" s="2"/>
     </row>
     <row r="974" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B974" s="3"/>
+      <c r="B974" s="2"/>
     </row>
     <row r="975" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B975" s="3"/>
+      <c r="B975" s="2"/>
     </row>
     <row r="976" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B976" s="3"/>
+      <c r="B976" s="2"/>
     </row>
     <row r="977" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B977" s="3"/>
+      <c r="B977" s="2"/>
     </row>
     <row r="978" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B978" s="3"/>
+      <c r="B978" s="2"/>
     </row>
     <row r="979" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B979" s="3"/>
+      <c r="B979" s="2"/>
     </row>
     <row r="980" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B980" s="3"/>
+      <c r="B980" s="2"/>
     </row>
     <row r="981" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B981" s="3"/>
+      <c r="B981" s="2"/>
     </row>
     <row r="982" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B982" s="3"/>
+      <c r="B982" s="2"/>
     </row>
     <row r="983" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B983" s="3"/>
+      <c r="B983" s="2"/>
     </row>
     <row r="984" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B984" s="3"/>
+      <c r="B984" s="2"/>
     </row>
     <row r="985" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B985" s="3"/>
+      <c r="B985" s="2"/>
     </row>
     <row r="986" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B986" s="3"/>
+      <c r="B986" s="2"/>
     </row>
     <row r="987" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B987" s="3"/>
+      <c r="B987" s="2"/>
     </row>
     <row r="988" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B988" s="3"/>
+      <c r="B988" s="2"/>
     </row>
     <row r="989" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B989" s="3"/>
+      <c r="B989" s="2"/>
     </row>
     <row r="990" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B990" s="3"/>
+      <c r="B990" s="2"/>
     </row>
     <row r="991" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B991" s="3"/>
+      <c r="B991" s="2"/>
     </row>
     <row r="992" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B992" s="3"/>
+      <c r="B992" s="2"/>
     </row>
     <row r="993" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B993" s="3"/>
+      <c r="B993" s="2"/>
     </row>
     <row r="994" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B994" s="3"/>
+      <c r="B994" s="2"/>
     </row>
     <row r="995" spans="2:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B995" s="3"/>
+      <c r="B995" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-chosen-filters-columns.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-chosen-filters-columns.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\runs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\OneDrive\Desktop\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\runs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B459D3-FC5A-45E3-8FA3-0955816D1909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E5A8DB-2D48-43FB-9886-AEDF5FCFECF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2960" yWindow="2960" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2185,7 +2185,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2196,6 +2196,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2418,13 +2421,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B995"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="116.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.5546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="116.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.54296875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2432,15 +2435,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="238" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2456,7 +2459,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2480,7 +2483,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2488,7 +2491,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2496,7 +2499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2512,7 +2515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
@@ -2520,7 +2523,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -2536,7 +2539,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -2544,7 +2547,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -2552,7 +2555,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
@@ -2560,7 +2563,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
@@ -2568,7 +2571,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
@@ -2576,7 +2579,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>24</v>
       </c>
@@ -2592,7 +2595,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
@@ -2608,7 +2611,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
@@ -2616,7 +2619,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>28</v>
       </c>
@@ -2624,7 +2627,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
@@ -2632,7 +2635,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>30</v>
       </c>
@@ -2640,7 +2643,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>31</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>32</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>33</v>
       </c>
@@ -2664,7 +2667,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>34</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>35</v>
       </c>
@@ -2680,7 +2683,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>36</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>37</v>
       </c>
@@ -2696,7 +2699,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>38</v>
       </c>
@@ -2704,7 +2707,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>39</v>
       </c>
@@ -2712,7 +2715,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>40</v>
       </c>
@@ -2720,7 +2723,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>41</v>
       </c>
@@ -2728,7 +2731,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>42</v>
       </c>
@@ -2736,7 +2739,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
@@ -2744,7 +2747,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>44</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>45</v>
       </c>
@@ -2760,7 +2763,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>46</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>47</v>
       </c>
@@ -2776,7 +2779,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>48</v>
       </c>
@@ -2784,7 +2787,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>50</v>
       </c>
@@ -2792,7 +2795,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>51</v>
       </c>
@@ -2800,7 +2803,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>52</v>
       </c>
@@ -2808,7 +2811,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>53</v>
       </c>
@@ -2816,7 +2819,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>54</v>
       </c>
@@ -2824,7 +2827,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>55</v>
       </c>
@@ -2832,7 +2835,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
@@ -2840,7 +2843,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>57</v>
       </c>
@@ -2848,7 +2851,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>58</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>59</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>61</v>
       </c>
@@ -2872,7 +2875,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>63</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>67</v>
       </c>
@@ -2896,7 +2899,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>69</v>
       </c>
@@ -2904,7 +2907,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
@@ -2912,7 +2915,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>72</v>
       </c>
@@ -2920,7 +2923,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>74</v>
       </c>
@@ -2928,7 +2931,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>75</v>
       </c>
@@ -2936,7 +2939,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>76</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>78</v>
       </c>
@@ -2952,7 +2955,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>79</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>81</v>
       </c>
@@ -2968,7 +2971,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>82</v>
       </c>
@@ -2976,7 +2979,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>83</v>
       </c>
@@ -2984,7 +2987,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>84</v>
       </c>
@@ -2992,7 +2995,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>86</v>
       </c>
@@ -3000,7 +3003,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>88</v>
       </c>
@@ -3008,7 +3011,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>90</v>
       </c>
@@ -3016,7 +3019,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>92</v>
       </c>
@@ -3024,7 +3027,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>93</v>
       </c>
@@ -3032,7 +3035,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>94</v>
       </c>
@@ -3040,7 +3043,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>95</v>
       </c>
@@ -3048,7 +3051,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>96</v>
       </c>
@@ -3056,7 +3059,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>97</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>98</v>
       </c>
@@ -3072,7 +3075,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>100</v>
       </c>
@@ -3080,7 +3083,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>102</v>
       </c>
@@ -3088,7 +3091,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>103</v>
       </c>
@@ -3096,7 +3099,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>104</v>
       </c>
@@ -3104,7 +3107,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>106</v>
       </c>
@@ -3112,7 +3115,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>107</v>
       </c>
@@ -3120,7 +3123,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>109</v>
       </c>
@@ -3128,7 +3131,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>110</v>
       </c>
@@ -3136,7 +3139,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>111</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>113</v>
       </c>
@@ -3152,7 +3155,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>114</v>
       </c>
@@ -3160,7 +3163,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>115</v>
       </c>
@@ -3168,7 +3171,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>117</v>
       </c>
@@ -3176,7 +3179,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>118</v>
       </c>
@@ -3184,7 +3187,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>119</v>
       </c>
@@ -3192,7 +3195,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>120</v>
       </c>
@@ -3200,7 +3203,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>122</v>
       </c>
@@ -3208,7 +3211,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>123</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>125</v>
       </c>
@@ -3224,7 +3227,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>127</v>
       </c>
